--- a/research/traditional_assets/database/data/croatia/croatia_information_services.xlsx
+++ b/research/traditional_assets/database/data/croatia/croatia_information_services.xlsx
@@ -1272,7 +1272,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1409,22 +1409,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.106241417399388</v>
+        <v>0.1060870828480691</v>
       </c>
       <c r="C2">
-        <v>399.9943222384949</v>
+        <v>396.8027135288685</v>
       </c>
       <c r="D2">
-        <v>344.2943222384949</v>
+        <v>345.1757135288685</v>
       </c>
       <c r="E2">
-        <v>-114.5</v>
+        <v>-110.427</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>4.073</v>
       </c>
       <c r="G2">
         <v>55.7</v>
@@ -1445,28 +1445,28 @@
         <v>33.2</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.2048719</v>
       </c>
       <c r="N2">
-        <v>33.2</v>
+        <v>32.9951281</v>
       </c>
       <c r="O2">
-        <v>5.976</v>
+        <v>5.939123058</v>
       </c>
       <c r="P2">
-        <v>27.224</v>
+        <v>27.056005042</v>
       </c>
       <c r="Q2">
-        <v>53.024</v>
+        <v>52.85600504200001</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.106241417399388</v>
+        <v>0.1067420432808779</v>
       </c>
       <c r="T2">
-        <v>1.01912912879999</v>
+        <v>1.027570400371868</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>162.0524825512918</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1491,22 +1491,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1060870828480691</v>
+        <v>0.1059327482967502</v>
       </c>
       <c r="C3">
-        <v>396.8027135288685</v>
+        <v>393.6156291136803</v>
       </c>
       <c r="D3">
-        <v>345.1757135288685</v>
+        <v>346.0616291136803</v>
       </c>
       <c r="E3">
-        <v>-110.427</v>
+        <v>-106.354</v>
       </c>
       <c r="F3">
-        <v>4.073</v>
+        <v>8.146000000000001</v>
       </c>
       <c r="G3">
         <v>55.7</v>
@@ -1527,28 +1527,28 @@
         <v>33.2</v>
       </c>
       <c r="M3">
-        <v>0.2048719</v>
+        <v>0.4097438</v>
       </c>
       <c r="N3">
-        <v>32.9951281</v>
+        <v>32.7902562</v>
       </c>
       <c r="O3">
-        <v>5.939123058</v>
+        <v>5.902246116</v>
       </c>
       <c r="P3">
-        <v>27.056005042</v>
+        <v>26.888010084</v>
       </c>
       <c r="Q3">
-        <v>52.85600504200001</v>
+        <v>52.688010084</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1067420432808779</v>
+        <v>0.107252886017092</v>
       </c>
       <c r="T3">
-        <v>1.027570400371868</v>
+        <v>1.036183942792153</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>162.0524825512918</v>
+        <v>81.0262412756459</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1573,22 +1573,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1059327482967502</v>
+        <v>0.1057784137454313</v>
       </c>
       <c r="C4">
-        <v>393.6156291136803</v>
+        <v>390.4331039182431</v>
       </c>
       <c r="D4">
-        <v>346.0616291136803</v>
+        <v>346.9521039182432</v>
       </c>
       <c r="E4">
-        <v>-106.354</v>
+        <v>-102.281</v>
       </c>
       <c r="F4">
-        <v>8.146000000000001</v>
+        <v>12.219</v>
       </c>
       <c r="G4">
         <v>55.7</v>
@@ -1609,28 +1609,28 @@
         <v>33.2</v>
       </c>
       <c r="M4">
-        <v>0.4097438</v>
+        <v>0.6146157</v>
       </c>
       <c r="N4">
-        <v>32.7902562</v>
+        <v>32.5853843</v>
       </c>
       <c r="O4">
-        <v>5.902246116</v>
+        <v>5.865369174</v>
       </c>
       <c r="P4">
-        <v>26.888010084</v>
+        <v>26.720015126</v>
       </c>
       <c r="Q4">
-        <v>52.688010084</v>
+        <v>52.520015126</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.107252886017092</v>
+        <v>0.1077742615932281</v>
       </c>
       <c r="T4">
-        <v>1.036183942792153</v>
+        <v>1.044975084025226</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>81.0262412756459</v>
+        <v>54.01749418376394</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1655,22 +1655,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1057784137454313</v>
+        <v>0.1056240791941124</v>
       </c>
       <c r="C5">
-        <v>390.4331039182431</v>
+        <v>387.2551732282717</v>
       </c>
       <c r="D5">
-        <v>346.9521039182432</v>
+        <v>347.8471732282717</v>
       </c>
       <c r="E5">
-        <v>-102.281</v>
+        <v>-98.208</v>
       </c>
       <c r="F5">
-        <v>12.219</v>
+        <v>16.292</v>
       </c>
       <c r="G5">
         <v>55.7</v>
@@ -1691,28 +1691,28 @@
         <v>33.2</v>
       </c>
       <c r="M5">
-        <v>0.6146157</v>
+        <v>0.8194876000000001</v>
       </c>
       <c r="N5">
-        <v>32.5853843</v>
+        <v>32.3805124</v>
       </c>
       <c r="O5">
-        <v>5.865369174</v>
+        <v>5.828492232</v>
       </c>
       <c r="P5">
-        <v>26.720015126</v>
+        <v>26.552020168</v>
       </c>
       <c r="Q5">
-        <v>52.520015126</v>
+        <v>52.352020168</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1077742615932281</v>
+        <v>0.1083064991605338</v>
       </c>
       <c r="T5">
-        <v>1.044975084025226</v>
+        <v>1.053949374033989</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>54.01749418376394</v>
+        <v>40.51312063782295</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1737,22 +1737,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1056240791941124</v>
+        <v>0.1054697446427935</v>
       </c>
       <c r="C6">
-        <v>387.2551732282717</v>
+        <v>384.0818726945441</v>
       </c>
       <c r="D6">
-        <v>347.8471732282717</v>
+        <v>348.7468726945442</v>
       </c>
       <c r="E6">
-        <v>-98.208</v>
+        <v>-94.13499999999999</v>
       </c>
       <c r="F6">
-        <v>16.292</v>
+        <v>20.365</v>
       </c>
       <c r="G6">
         <v>55.7</v>
@@ -1773,28 +1773,28 @@
         <v>33.2</v>
       </c>
       <c r="M6">
-        <v>0.8194876000000001</v>
+        <v>1.0243595</v>
       </c>
       <c r="N6">
-        <v>32.3805124</v>
+        <v>32.1756405</v>
       </c>
       <c r="O6">
-        <v>5.828492232</v>
+        <v>5.79161529</v>
       </c>
       <c r="P6">
-        <v>26.552020168</v>
+        <v>26.38402521</v>
       </c>
       <c r="Q6">
-        <v>52.352020168</v>
+        <v>52.18402521</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1083064991605338</v>
+        <v>0.1088499417292563</v>
       </c>
       <c r="T6">
-        <v>1.053949374033989</v>
+        <v>1.063112596463989</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>40.51312063782295</v>
+        <v>32.41049651025835</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1819,22 +1819,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1054697446427935</v>
+        <v>0.1053154100914746</v>
       </c>
       <c r="C7">
-        <v>384.0818726945441</v>
+        <v>380.9132383376348</v>
       </c>
       <c r="D7">
-        <v>348.7468726945442</v>
+        <v>349.6512383376348</v>
       </c>
       <c r="E7">
-        <v>-94.13499999999999</v>
+        <v>-90.062</v>
       </c>
       <c r="F7">
-        <v>20.365</v>
+        <v>24.438</v>
       </c>
       <c r="G7">
         <v>55.7</v>
@@ -1855,28 +1855,28 @@
         <v>33.2</v>
       </c>
       <c r="M7">
-        <v>1.0243595</v>
+        <v>1.2292314</v>
       </c>
       <c r="N7">
-        <v>32.1756405</v>
+        <v>31.9707686</v>
       </c>
       <c r="O7">
-        <v>5.79161529</v>
+        <v>5.754738348</v>
       </c>
       <c r="P7">
-        <v>26.38402521</v>
+        <v>26.216030252</v>
       </c>
       <c r="Q7">
-        <v>52.18402521</v>
+        <v>52.01603025200001</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1088499417292563</v>
+        <v>0.109404946905824</v>
       </c>
       <c r="T7">
-        <v>1.063112596463989</v>
+        <v>1.072470781073351</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>32.41049651025835</v>
+        <v>27.00874709188197</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1901,22 +1901,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1053154100914746</v>
+        <v>0.1051610755401557</v>
       </c>
       <c r="C8">
-        <v>380.9132383376348</v>
+        <v>377.7493065527217</v>
       </c>
       <c r="D8">
-        <v>349.6512383376348</v>
+        <v>350.5603065527218</v>
       </c>
       <c r="E8">
-        <v>-90.062</v>
+        <v>-85.989</v>
       </c>
       <c r="F8">
-        <v>24.438</v>
+        <v>28.511</v>
       </c>
       <c r="G8">
         <v>55.7</v>
@@ -1937,28 +1937,28 @@
         <v>33.2</v>
       </c>
       <c r="M8">
-        <v>1.2292314</v>
+        <v>1.4341033</v>
       </c>
       <c r="N8">
-        <v>31.9707686</v>
+        <v>31.7658967</v>
       </c>
       <c r="O8">
-        <v>5.754738348</v>
+        <v>5.717861406</v>
       </c>
       <c r="P8">
-        <v>26.216030252</v>
+        <v>26.048035294</v>
       </c>
       <c r="Q8">
-        <v>52.01603025200001</v>
+        <v>51.848035294</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.109404946905824</v>
+        <v>0.1099718876775868</v>
       </c>
       <c r="T8">
-        <v>1.072470781073351</v>
+        <v>1.082030216964634</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>27.00874709188197</v>
+        <v>23.15035465018455</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1983,22 +1983,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1051610755401557</v>
+        <v>0.1050067409888368</v>
       </c>
       <c r="C9">
-        <v>377.7493065527218</v>
+        <v>374.5901141144694</v>
       </c>
       <c r="D9">
-        <v>350.5603065527218</v>
+        <v>351.4741141144694</v>
       </c>
       <c r="E9">
-        <v>-85.989</v>
+        <v>-81.916</v>
       </c>
       <c r="F9">
-        <v>28.511</v>
+        <v>32.584</v>
       </c>
       <c r="G9">
         <v>55.7</v>
@@ -2019,28 +2019,28 @@
         <v>33.2</v>
       </c>
       <c r="M9">
-        <v>1.4341033</v>
+        <v>1.6389752</v>
       </c>
       <c r="N9">
-        <v>31.7658967</v>
+        <v>31.5610248</v>
       </c>
       <c r="O9">
-        <v>5.717861406</v>
+        <v>5.680984464</v>
       </c>
       <c r="P9">
-        <v>26.048035294</v>
+        <v>25.880040336</v>
       </c>
       <c r="Q9">
-        <v>51.848035294</v>
+        <v>51.680040336</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1099718876775868</v>
+        <v>0.1105511532487357</v>
       </c>
       <c r="T9">
-        <v>1.082030216964634</v>
+        <v>1.091797466679641</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>23.15035465018454</v>
+        <v>20.25656031891148</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2065,22 +2065,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1050067409888368</v>
+        <v>0.1048524064375179</v>
       </c>
       <c r="C10">
-        <v>374.5901141144694</v>
+        <v>371.4356981819867</v>
       </c>
       <c r="D10">
-        <v>351.4741141144694</v>
+        <v>352.3926981819866</v>
       </c>
       <c r="E10">
-        <v>-81.916</v>
+        <v>-77.843</v>
       </c>
       <c r="F10">
-        <v>32.584</v>
+        <v>36.657</v>
       </c>
       <c r="G10">
         <v>55.7</v>
@@ -2101,28 +2101,28 @@
         <v>33.2</v>
       </c>
       <c r="M10">
-        <v>1.6389752</v>
+        <v>1.8438471</v>
       </c>
       <c r="N10">
-        <v>31.5610248</v>
+        <v>31.3561529</v>
       </c>
       <c r="O10">
-        <v>5.680984464</v>
+        <v>5.644107522000001</v>
       </c>
       <c r="P10">
-        <v>25.880040336</v>
+        <v>25.71204537800001</v>
       </c>
       <c r="Q10">
-        <v>51.680040336</v>
+        <v>51.51204537800001</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1105511532487357</v>
+        <v>0.1111431499313384</v>
       </c>
       <c r="T10">
-        <v>1.091797466679641</v>
+        <v>1.101779381223549</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>20.25656031891148</v>
+        <v>18.00583139458799</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2147,22 +2147,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1048524064375179</v>
+        <v>0.104698071886199</v>
       </c>
       <c r="C11">
-        <v>371.4356981819867</v>
+        <v>368.2860963038651</v>
       </c>
       <c r="D11">
-        <v>352.3926981819866</v>
+        <v>353.3160963038651</v>
       </c>
       <c r="E11">
-        <v>-77.843</v>
+        <v>-73.77000000000001</v>
       </c>
       <c r="F11">
-        <v>36.657</v>
+        <v>40.73</v>
       </c>
       <c r="G11">
         <v>55.7</v>
@@ -2183,28 +2183,28 @@
         <v>33.2</v>
       </c>
       <c r="M11">
-        <v>1.8438471</v>
+        <v>2.048719</v>
       </c>
       <c r="N11">
-        <v>31.3561529</v>
+        <v>31.151281</v>
       </c>
       <c r="O11">
-        <v>5.644107522000001</v>
+        <v>5.60723058</v>
       </c>
       <c r="P11">
-        <v>25.71204537800001</v>
+        <v>25.54405042</v>
       </c>
       <c r="Q11">
-        <v>51.51204537800001</v>
+        <v>51.34405042</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1111431499313384</v>
+        <v>0.1117483020957767</v>
       </c>
       <c r="T11">
-        <v>1.101779381223549</v>
+        <v>1.111983116090655</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2221,7 +2221,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>18.00583139458799</v>
+        <v>16.20524825512918</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2229,22 +2229,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.104698071886199</v>
+        <v>0.1045437373348801</v>
       </c>
       <c r="C12">
-        <v>368.286096303865</v>
+        <v>365.141346423294</v>
       </c>
       <c r="D12">
-        <v>353.316096303865</v>
+        <v>354.244346423294</v>
       </c>
       <c r="E12">
-        <v>-73.77</v>
+        <v>-69.697</v>
       </c>
       <c r="F12">
-        <v>40.73</v>
+        <v>44.803</v>
       </c>
       <c r="G12">
         <v>55.7</v>
@@ -2265,28 +2265,28 @@
         <v>33.2</v>
       </c>
       <c r="M12">
-        <v>2.048719</v>
+        <v>2.2535909</v>
       </c>
       <c r="N12">
-        <v>31.151281</v>
+        <v>30.9464091</v>
       </c>
       <c r="O12">
-        <v>5.60723058</v>
+        <v>5.570353638</v>
       </c>
       <c r="P12">
-        <v>25.54405042</v>
+        <v>25.376055462</v>
       </c>
       <c r="Q12">
-        <v>51.34405042</v>
+        <v>51.17605546200001</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1117483020957767</v>
+        <v>0.1123670531852586</v>
       </c>
       <c r="T12">
-        <v>1.111983116090655</v>
+        <v>1.122416148370505</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>16.20524825512918</v>
+        <v>14.73204386829926</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2311,22 +2311,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1045437373348801</v>
+        <v>0.1043894027835612</v>
       </c>
       <c r="C13">
-        <v>365.141346423294</v>
+        <v>362.0014868832585</v>
       </c>
       <c r="D13">
-        <v>354.244346423294</v>
+        <v>355.1774868832584</v>
       </c>
       <c r="E13">
-        <v>-69.697</v>
+        <v>-65.624</v>
       </c>
       <c r="F13">
-        <v>44.803</v>
+        <v>48.876</v>
       </c>
       <c r="G13">
         <v>55.7</v>
@@ -2347,28 +2347,28 @@
         <v>33.2</v>
       </c>
       <c r="M13">
-        <v>2.2535909</v>
+        <v>2.4584628</v>
       </c>
       <c r="N13">
-        <v>30.9464091</v>
+        <v>30.7415372</v>
       </c>
       <c r="O13">
-        <v>5.570353638</v>
+        <v>5.533476696</v>
       </c>
       <c r="P13">
-        <v>25.376055462</v>
+        <v>25.208060504</v>
       </c>
       <c r="Q13">
-        <v>51.17605546200001</v>
+        <v>51.008060504</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1123670531852586</v>
+        <v>0.1129998667995014</v>
       </c>
       <c r="T13">
-        <v>1.122416148370505</v>
+        <v>1.133086295020352</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>14.73204386829926</v>
+        <v>13.50437354594099</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1043894027835612</v>
+        <v>0.1043949682322423</v>
       </c>
       <c r="C14">
-        <v>362.0014868832585</v>
+        <v>357.8947515278932</v>
       </c>
       <c r="D14">
-        <v>355.1774868832584</v>
+        <v>355.1437515278932</v>
       </c>
       <c r="E14">
-        <v>-65.624</v>
+        <v>-61.55099999999999</v>
       </c>
       <c r="F14">
-        <v>48.876</v>
+        <v>52.94900000000001</v>
       </c>
       <c r="G14">
         <v>55.7</v>
@@ -2429,45 +2429,45 @@
         <v>33.2</v>
       </c>
       <c r="M14">
-        <v>2.4584628</v>
+        <v>2.7427582</v>
       </c>
       <c r="N14">
-        <v>30.7415372</v>
+        <v>30.4572418</v>
       </c>
       <c r="O14">
-        <v>5.533476696</v>
+        <v>5.482303524</v>
       </c>
       <c r="P14">
-        <v>25.208060504</v>
+        <v>24.974938276</v>
       </c>
       <c r="Q14">
-        <v>51.008060504</v>
+        <v>50.774938276</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1129998667995014</v>
+        <v>0.1136472278531521</v>
       </c>
       <c r="T14">
-        <v>1.133086295020352</v>
+        <v>1.144001732397781</v>
       </c>
       <c r="U14">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V14">
         <v>0.18</v>
       </c>
       <c r="W14">
-        <v>0.041246</v>
+        <v>0.042476</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y14">
-        <v>13.50437354594099</v>
+        <v>12.10460331501333</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2475,22 +2475,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1043949682322423</v>
+        <v>0.1042529336809234</v>
       </c>
       <c r="C15">
-        <v>357.8947515278932</v>
+        <v>354.6847139187515</v>
       </c>
       <c r="D15">
-        <v>355.1437515278932</v>
+        <v>356.0067139187515</v>
       </c>
       <c r="E15">
-        <v>-61.55099999999999</v>
+        <v>-57.47799999999999</v>
       </c>
       <c r="F15">
-        <v>52.94900000000001</v>
+        <v>57.02200000000001</v>
       </c>
       <c r="G15">
         <v>55.7</v>
@@ -2511,28 +2511,28 @@
         <v>33.2</v>
       </c>
       <c r="M15">
-        <v>2.7427582</v>
+        <v>2.9537396</v>
       </c>
       <c r="N15">
-        <v>30.4572418</v>
+        <v>30.2462604</v>
       </c>
       <c r="O15">
-        <v>5.482303524</v>
+        <v>5.444326872</v>
       </c>
       <c r="P15">
-        <v>24.974938276</v>
+        <v>24.801933528</v>
       </c>
       <c r="Q15">
-        <v>50.774938276</v>
+        <v>50.601933528</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1136472278531521</v>
+        <v>0.1143096438150272</v>
       </c>
       <c r="T15">
-        <v>1.144001732397781</v>
+        <v>1.155171017156081</v>
       </c>
       <c r="U15">
         <v>0.0518</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>12.10460331501333</v>
+        <v>11.23998879251238</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2557,22 +2557,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1042529336809234</v>
+        <v>0.1041108991296045</v>
       </c>
       <c r="C16">
-        <v>354.6847139187515</v>
+        <v>351.4788803427434</v>
       </c>
       <c r="D16">
-        <v>356.0067139187515</v>
+        <v>356.8738803427435</v>
       </c>
       <c r="E16">
-        <v>-57.47799999999999</v>
+        <v>-53.40499999999999</v>
       </c>
       <c r="F16">
-        <v>57.02200000000001</v>
+        <v>61.09500000000001</v>
       </c>
       <c r="G16">
         <v>55.7</v>
@@ -2593,28 +2593,28 @@
         <v>33.2</v>
       </c>
       <c r="M16">
-        <v>2.9537396</v>
+        <v>3.164721000000001</v>
       </c>
       <c r="N16">
-        <v>30.2462604</v>
+        <v>30.035279</v>
       </c>
       <c r="O16">
-        <v>5.444326872</v>
+        <v>5.40635022</v>
       </c>
       <c r="P16">
-        <v>24.801933528</v>
+        <v>24.62892878</v>
       </c>
       <c r="Q16">
-        <v>50.601933528</v>
+        <v>50.42892878000001</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1143096438150272</v>
+        <v>0.1149876460348288</v>
       </c>
       <c r="T16">
-        <v>1.155171017156081</v>
+        <v>1.166603108614576</v>
       </c>
       <c r="U16">
         <v>0.0518</v>
@@ -2631,7 +2631,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>11.23998879251238</v>
+        <v>10.49065620634489</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2639,22 +2639,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1041108991296045</v>
+        <v>0.1039688645782856</v>
       </c>
       <c r="C17">
-        <v>351.4788803427434</v>
+        <v>348.2772815956197</v>
       </c>
       <c r="D17">
-        <v>356.8738803427435</v>
+        <v>357.7452815956198</v>
       </c>
       <c r="E17">
-        <v>-53.405</v>
+        <v>-49.33199999999999</v>
       </c>
       <c r="F17">
-        <v>61.095</v>
+        <v>65.16800000000001</v>
       </c>
       <c r="G17">
         <v>55.7</v>
@@ -2675,28 +2675,28 @@
         <v>33.2</v>
       </c>
       <c r="M17">
-        <v>3.164721</v>
+        <v>3.3757024</v>
       </c>
       <c r="N17">
-        <v>30.035279</v>
+        <v>29.8242976</v>
       </c>
       <c r="O17">
-        <v>5.40635022</v>
+        <v>5.368373568</v>
       </c>
       <c r="P17">
-        <v>24.62892878</v>
+        <v>24.455924032</v>
       </c>
       <c r="Q17">
-        <v>50.42892878000001</v>
+        <v>50.255924032</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1149876460348288</v>
+        <v>0.1156817911646257</v>
       </c>
       <c r="T17">
-        <v>1.166603108614576</v>
+        <v>1.178307392726845</v>
       </c>
       <c r="U17">
         <v>0.0518</v>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>10.49065620634489</v>
+        <v>9.834990193448332</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2721,22 +2721,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1039688645782856</v>
+        <v>0.1040638100269667</v>
       </c>
       <c r="C18">
-        <v>348.2772815956197</v>
+        <v>343.6213075975423</v>
       </c>
       <c r="D18">
-        <v>357.7452815956198</v>
+        <v>357.1623075975424</v>
       </c>
       <c r="E18">
-        <v>-49.33199999999999</v>
+        <v>-45.25899999999999</v>
       </c>
       <c r="F18">
-        <v>65.16800000000001</v>
+        <v>69.24100000000001</v>
       </c>
       <c r="G18">
         <v>55.7</v>
@@ -2757,45 +2757,45 @@
         <v>33.2</v>
       </c>
       <c r="M18">
-        <v>3.3757024</v>
+        <v>3.704393500000001</v>
       </c>
       <c r="N18">
-        <v>29.8242976</v>
+        <v>29.4956065</v>
       </c>
       <c r="O18">
-        <v>5.368373568</v>
+        <v>5.30920917</v>
       </c>
       <c r="P18">
-        <v>24.455924032</v>
+        <v>24.18639733</v>
       </c>
       <c r="Q18">
-        <v>50.255924032</v>
+        <v>49.98639733</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1156817911646257</v>
+        <v>0.1163926626830924</v>
       </c>
       <c r="T18">
-        <v>1.178307392726845</v>
+        <v>1.190293707781578</v>
       </c>
       <c r="U18">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V18">
         <v>0.18</v>
       </c>
       <c r="W18">
-        <v>0.042476</v>
+        <v>0.04387</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y18">
-        <v>9.834990193448332</v>
+        <v>8.962330810698161</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2803,22 +2803,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1040638100269667</v>
+        <v>0.1039357154756478</v>
       </c>
       <c r="C19">
-        <v>343.6213075975423</v>
+        <v>340.3352686793044</v>
       </c>
       <c r="D19">
-        <v>357.1623075975424</v>
+        <v>357.9492686793044</v>
       </c>
       <c r="E19">
-        <v>-45.25899999999999</v>
+        <v>-41.18599999999999</v>
       </c>
       <c r="F19">
-        <v>69.24100000000001</v>
+        <v>73.31400000000001</v>
       </c>
       <c r="G19">
         <v>55.7</v>
@@ -2839,28 +2839,28 @@
         <v>33.2</v>
       </c>
       <c r="M19">
-        <v>3.704393500000001</v>
+        <v>3.922299</v>
       </c>
       <c r="N19">
-        <v>29.4956065</v>
+        <v>29.277701</v>
       </c>
       <c r="O19">
-        <v>5.30920917</v>
+        <v>5.269986180000001</v>
       </c>
       <c r="P19">
-        <v>24.18639733</v>
+        <v>24.00771482</v>
       </c>
       <c r="Q19">
-        <v>49.98639733</v>
+        <v>49.80771482</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1163926626830924</v>
+        <v>0.1171208725312778</v>
       </c>
       <c r="T19">
-        <v>1.190293707781578</v>
+        <v>1.202572371983988</v>
       </c>
       <c r="U19">
         <v>0.0535</v>
@@ -2877,7 +2877,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>8.962330810698161</v>
+        <v>8.464423543437153</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2885,22 +2885,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1039357154756478</v>
+        <v>0.1038076209243289</v>
       </c>
       <c r="C20">
-        <v>340.3352686793044</v>
+        <v>337.0527053535857</v>
       </c>
       <c r="D20">
-        <v>357.9492686793044</v>
+        <v>358.7397053535857</v>
       </c>
       <c r="E20">
-        <v>-41.18600000000001</v>
+        <v>-37.113</v>
       </c>
       <c r="F20">
-        <v>73.31399999999999</v>
+        <v>77.387</v>
       </c>
       <c r="G20">
         <v>55.7</v>
@@ -2921,28 +2921,28 @@
         <v>33.2</v>
       </c>
       <c r="M20">
-        <v>3.922299</v>
+        <v>4.1402045</v>
       </c>
       <c r="N20">
-        <v>29.277701</v>
+        <v>29.0597955</v>
       </c>
       <c r="O20">
-        <v>5.269986180000001</v>
+        <v>5.23076319</v>
       </c>
       <c r="P20">
-        <v>24.00771482</v>
+        <v>23.82903231</v>
       </c>
       <c r="Q20">
-        <v>49.80771482</v>
+        <v>49.62903231</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1171208725312778</v>
+        <v>0.1178670628695419</v>
       </c>
       <c r="T20">
-        <v>1.202572371983988</v>
+        <v>1.215154213080284</v>
       </c>
       <c r="U20">
         <v>0.0535</v>
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>8.464423543437153</v>
+        <v>8.018927567466775</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2967,22 +2967,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1038076209243289</v>
+        <v>0.10367952637301</v>
       </c>
       <c r="C21">
-        <v>337.0527053535857</v>
+        <v>333.773640696135</v>
       </c>
       <c r="D21">
-        <v>358.7397053535857</v>
+        <v>359.533640696135</v>
       </c>
       <c r="E21">
-        <v>-37.113</v>
+        <v>-33.03999999999999</v>
       </c>
       <c r="F21">
-        <v>77.387</v>
+        <v>81.46000000000001</v>
       </c>
       <c r="G21">
         <v>55.7</v>
@@ -3003,28 +3003,28 @@
         <v>33.2</v>
       </c>
       <c r="M21">
-        <v>4.1402045</v>
+        <v>4.35811</v>
       </c>
       <c r="N21">
-        <v>29.0597955</v>
+        <v>28.84189</v>
       </c>
       <c r="O21">
-        <v>5.23076319</v>
+        <v>5.1915402</v>
       </c>
       <c r="P21">
-        <v>23.82903231</v>
+        <v>23.6503498</v>
       </c>
       <c r="Q21">
-        <v>49.62903231</v>
+        <v>49.4503498</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1178670628695419</v>
+        <v>0.1186319079662625</v>
       </c>
       <c r="T21">
-        <v>1.215154213080284</v>
+        <v>1.228050600203987</v>
       </c>
       <c r="U21">
         <v>0.0535</v>
@@ -3041,7 +3041,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>8.018927567466775</v>
+        <v>7.617981189093438</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3049,22 +3049,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.10367952637301</v>
+        <v>0.1036891918216911</v>
       </c>
       <c r="C22">
-        <v>333.773640696135</v>
+        <v>329.6406112874678</v>
       </c>
       <c r="D22">
-        <v>359.533640696135</v>
+        <v>359.4736112874679</v>
       </c>
       <c r="E22">
-        <v>-33.03999999999999</v>
+        <v>-28.96699999999998</v>
       </c>
       <c r="F22">
-        <v>81.46000000000001</v>
+        <v>85.53300000000002</v>
       </c>
       <c r="G22">
         <v>55.7</v>
@@ -3085,45 +3085,45 @@
         <v>33.2</v>
       </c>
       <c r="M22">
-        <v>4.35811</v>
+        <v>4.644441900000001</v>
       </c>
       <c r="N22">
-        <v>28.84189</v>
+        <v>28.5555581</v>
       </c>
       <c r="O22">
-        <v>5.1915402</v>
+        <v>5.140000458</v>
       </c>
       <c r="P22">
-        <v>23.6503498</v>
+        <v>23.415557642</v>
       </c>
       <c r="Q22">
-        <v>49.4503498</v>
+        <v>49.21555764200001</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1186319079662625</v>
+        <v>0.1194161162299888</v>
       </c>
       <c r="T22">
-        <v>1.228050600203987</v>
+        <v>1.241273478140949</v>
       </c>
       <c r="U22">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V22">
         <v>0.18</v>
       </c>
       <c r="W22">
-        <v>0.04387</v>
+        <v>0.044526</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y22">
-        <v>7.617981189093438</v>
+        <v>7.148329275041635</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3131,22 +3131,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1036891918216911</v>
+        <v>0.1035676572703722</v>
       </c>
       <c r="C23">
-        <v>329.6406112874678</v>
+        <v>326.3238902526045</v>
       </c>
       <c r="D23">
-        <v>359.4736112874679</v>
+        <v>360.2298902526045</v>
       </c>
       <c r="E23">
-        <v>-28.967</v>
+        <v>-24.89399999999999</v>
       </c>
       <c r="F23">
-        <v>85.533</v>
+        <v>89.60600000000001</v>
       </c>
       <c r="G23">
         <v>55.7</v>
@@ -3167,28 +3167,28 @@
         <v>33.2</v>
       </c>
       <c r="M23">
-        <v>4.6444419</v>
+        <v>4.865605800000001</v>
       </c>
       <c r="N23">
-        <v>28.5555581</v>
+        <v>28.3343942</v>
       </c>
       <c r="O23">
-        <v>5.140000458</v>
+        <v>5.100190956</v>
       </c>
       <c r="P23">
-        <v>23.415557642</v>
+        <v>23.234203244</v>
       </c>
       <c r="Q23">
-        <v>49.21555764200001</v>
+        <v>49.034203244</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1194161162299888</v>
+        <v>0.1202204323979131</v>
       </c>
       <c r="T23">
-        <v>1.241273478140949</v>
+        <v>1.254835404230141</v>
       </c>
       <c r="U23">
         <v>0.0543</v>
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>7.148329275041636</v>
+        <v>6.823405217085198</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3213,22 +3213,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1035676572703722</v>
+        <v>0.1034461227190533</v>
       </c>
       <c r="C24">
-        <v>326.3238902526045</v>
+        <v>323.0103581234425</v>
       </c>
       <c r="D24">
-        <v>360.2298902526045</v>
+        <v>360.9893581234425</v>
       </c>
       <c r="E24">
-        <v>-24.89399999999999</v>
+        <v>-20.821</v>
       </c>
       <c r="F24">
-        <v>89.60600000000001</v>
+        <v>93.679</v>
       </c>
       <c r="G24">
         <v>55.7</v>
@@ -3249,28 +3249,28 @@
         <v>33.2</v>
       </c>
       <c r="M24">
-        <v>4.865605800000001</v>
+        <v>5.086769700000001</v>
       </c>
       <c r="N24">
-        <v>28.3343942</v>
+        <v>28.1132303</v>
       </c>
       <c r="O24">
-        <v>5.100190956</v>
+        <v>5.060381454</v>
       </c>
       <c r="P24">
-        <v>23.234203244</v>
+        <v>23.052848846</v>
       </c>
       <c r="Q24">
-        <v>49.034203244</v>
+        <v>48.852848846</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1202204323979131</v>
+        <v>0.1210456398948745</v>
       </c>
       <c r="T24">
-        <v>1.254835404230141</v>
+        <v>1.268749588139831</v>
       </c>
       <c r="U24">
         <v>0.0543</v>
@@ -3287,7 +3287,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>6.823405217085198</v>
+        <v>6.526735425038016</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3295,22 +3295,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1034461227190533</v>
+        <v>0.1033245881677344</v>
       </c>
       <c r="C25">
-        <v>323.0103581234425</v>
+        <v>319.7000351119765</v>
       </c>
       <c r="D25">
-        <v>360.9893581234425</v>
+        <v>361.7520351119766</v>
       </c>
       <c r="E25">
-        <v>-20.821</v>
+        <v>-16.74799999999999</v>
       </c>
       <c r="F25">
-        <v>93.679</v>
+        <v>97.75200000000001</v>
       </c>
       <c r="G25">
         <v>55.7</v>
@@ -3331,28 +3331,28 @@
         <v>33.2</v>
       </c>
       <c r="M25">
-        <v>5.086769700000001</v>
+        <v>5.307933600000001</v>
       </c>
       <c r="N25">
-        <v>28.1132303</v>
+        <v>27.8920664</v>
       </c>
       <c r="O25">
-        <v>5.060381454</v>
+        <v>5.020571952</v>
       </c>
       <c r="P25">
-        <v>23.052848846</v>
+        <v>22.871494448</v>
       </c>
       <c r="Q25">
-        <v>48.852848846</v>
+        <v>48.671494448</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1210456398948745</v>
+        <v>0.1218925633785979</v>
       </c>
       <c r="T25">
-        <v>1.268749588139831</v>
+        <v>1.283029934783987</v>
       </c>
       <c r="U25">
         <v>0.0543</v>
@@ -3369,7 +3369,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>6.526735425038016</v>
+        <v>6.254788115661431</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3377,22 +3377,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1033245881677344</v>
+        <v>0.1034080536164155</v>
       </c>
       <c r="C26">
-        <v>319.7000351119765</v>
+        <v>315.1029105490645</v>
       </c>
       <c r="D26">
-        <v>361.7520351119766</v>
+        <v>361.2279105490645</v>
       </c>
       <c r="E26">
-        <v>-16.748</v>
+        <v>-12.675</v>
       </c>
       <c r="F26">
-        <v>97.752</v>
+        <v>101.825</v>
       </c>
       <c r="G26">
         <v>55.7</v>
@@ -3413,45 +3413,45 @@
         <v>33.2</v>
       </c>
       <c r="M26">
-        <v>5.3079336</v>
+        <v>5.6309225</v>
       </c>
       <c r="N26">
-        <v>27.8920664</v>
+        <v>27.5690775</v>
       </c>
       <c r="O26">
-        <v>5.020571952000001</v>
+        <v>4.96243395</v>
       </c>
       <c r="P26">
-        <v>22.871494448</v>
+        <v>22.60664355</v>
       </c>
       <c r="Q26">
-        <v>48.671494448</v>
+        <v>48.40664355</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1218925633785979</v>
+        <v>0.122762071488554</v>
       </c>
       <c r="T26">
-        <v>1.283029934783987</v>
+        <v>1.297691090671987</v>
       </c>
       <c r="U26">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V26">
         <v>0.18</v>
       </c>
       <c r="W26">
-        <v>0.044526</v>
+        <v>0.045346</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y26">
-        <v>6.254788115661433</v>
+        <v>5.896014374198899</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1034080536164155</v>
+        <v>0.1032947190650966</v>
       </c>
       <c r="C27">
-        <v>315.1029105490645</v>
+        <v>311.7419690447252</v>
       </c>
       <c r="D27">
-        <v>361.2279105490645</v>
+        <v>361.9399690447253</v>
       </c>
       <c r="E27">
-        <v>-12.675</v>
+        <v>-8.60199999999999</v>
       </c>
       <c r="F27">
-        <v>101.825</v>
+        <v>105.898</v>
       </c>
       <c r="G27">
         <v>55.7</v>
@@ -3495,28 +3495,28 @@
         <v>33.2</v>
       </c>
       <c r="M27">
-        <v>5.6309225</v>
+        <v>5.856159400000001</v>
       </c>
       <c r="N27">
-        <v>27.5690775</v>
+        <v>27.3438406</v>
       </c>
       <c r="O27">
-        <v>4.96243395</v>
+        <v>4.921891308</v>
       </c>
       <c r="P27">
-        <v>22.60664355</v>
+        <v>22.421949292</v>
       </c>
       <c r="Q27">
-        <v>48.40664355</v>
+        <v>48.22194929200001</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.122762071488554</v>
+        <v>0.1236550798176982</v>
       </c>
       <c r="T27">
-        <v>1.297691090671987</v>
+        <v>1.312748494016419</v>
       </c>
       <c r="U27">
         <v>0.0553</v>
@@ -3533,7 +3533,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>5.896014374198899</v>
+        <v>5.669244590575864</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3541,22 +3541,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1032947190650966</v>
+        <v>0.1031813845137777</v>
       </c>
       <c r="C28">
-        <v>311.7419690447252</v>
+        <v>308.3838403282199</v>
       </c>
       <c r="D28">
-        <v>361.9399690447253</v>
+        <v>362.6548403282199</v>
       </c>
       <c r="E28">
-        <v>-8.60199999999999</v>
+        <v>-4.528999999999996</v>
       </c>
       <c r="F28">
-        <v>105.898</v>
+        <v>109.971</v>
       </c>
       <c r="G28">
         <v>55.7</v>
@@ -3577,28 +3577,28 @@
         <v>33.2</v>
       </c>
       <c r="M28">
-        <v>5.856159400000001</v>
+        <v>6.081396300000001</v>
       </c>
       <c r="N28">
-        <v>27.3438406</v>
+        <v>27.1186037</v>
       </c>
       <c r="O28">
-        <v>4.921891308</v>
+        <v>4.881348666</v>
       </c>
       <c r="P28">
-        <v>22.421949292</v>
+        <v>22.237255034</v>
       </c>
       <c r="Q28">
-        <v>48.22194929200001</v>
+        <v>48.037255034</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1236550798176982</v>
+        <v>0.1245725541284627</v>
       </c>
       <c r="T28">
-        <v>1.312748494016419</v>
+        <v>1.328218428959329</v>
       </c>
       <c r="U28">
         <v>0.0553</v>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>5.669244590575864</v>
+        <v>5.459272568702684</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3623,22 +3623,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1031813845137777</v>
+        <v>0.1030680499624588</v>
       </c>
       <c r="C29">
-        <v>308.3838403282199</v>
+        <v>305.0285410992286</v>
       </c>
       <c r="D29">
-        <v>362.6548403282199</v>
+        <v>363.3725410992287</v>
       </c>
       <c r="E29">
-        <v>-4.528999999999996</v>
+        <v>-0.4559999999999889</v>
       </c>
       <c r="F29">
-        <v>109.971</v>
+        <v>114.044</v>
       </c>
       <c r="G29">
         <v>55.7</v>
@@ -3659,28 +3659,28 @@
         <v>33.2</v>
       </c>
       <c r="M29">
-        <v>6.081396300000001</v>
+        <v>6.306633200000001</v>
       </c>
       <c r="N29">
-        <v>27.1186037</v>
+        <v>26.8933668</v>
       </c>
       <c r="O29">
-        <v>4.881348666</v>
+        <v>4.840806024</v>
       </c>
       <c r="P29">
-        <v>22.237255034</v>
+        <v>22.052560776</v>
       </c>
       <c r="Q29">
-        <v>48.037255034</v>
+        <v>47.852560776</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1245725541284627</v>
+        <v>0.1255155138367484</v>
       </c>
       <c r="T29">
-        <v>1.328218428959329</v>
+        <v>1.34411808431732</v>
       </c>
       <c r="U29">
         <v>0.0553</v>
@@ -3697,7 +3697,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>5.459272568702684</v>
+        <v>5.264298548391873</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3705,22 +3705,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1030680499624588</v>
+        <v>0.1029547154111399</v>
       </c>
       <c r="C30">
-        <v>305.0285410992286</v>
+        <v>301.6760881898904</v>
       </c>
       <c r="D30">
-        <v>363.3725410992287</v>
+        <v>364.0930881898904</v>
       </c>
       <c r="E30">
-        <v>-0.4559999999999889</v>
+        <v>3.617000000000019</v>
       </c>
       <c r="F30">
-        <v>114.044</v>
+        <v>118.117</v>
       </c>
       <c r="G30">
         <v>55.7</v>
@@ -3741,28 +3741,28 @@
         <v>33.2</v>
       </c>
       <c r="M30">
-        <v>6.306633200000001</v>
+        <v>6.531870100000002</v>
       </c>
       <c r="N30">
-        <v>26.8933668</v>
+        <v>26.6681299</v>
       </c>
       <c r="O30">
-        <v>4.840806024</v>
+        <v>4.800263382</v>
       </c>
       <c r="P30">
-        <v>22.052560776</v>
+        <v>21.867866518</v>
       </c>
       <c r="Q30">
-        <v>47.852560776</v>
+        <v>47.667866518</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1255155138367484</v>
+        <v>0.1264850357903379</v>
       </c>
       <c r="T30">
-        <v>1.34411808431732</v>
+        <v>1.360465617291028</v>
       </c>
       <c r="U30">
         <v>0.0553</v>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>5.264298548391873</v>
+        <v>5.082771012240429</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3787,22 +3787,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1029547154111399</v>
+        <v>0.102841380859821</v>
       </c>
       <c r="C31">
-        <v>301.6760881898905</v>
+        <v>298.3264985661175</v>
       </c>
       <c r="D31">
-        <v>364.0930881898905</v>
+        <v>364.8164985661175</v>
       </c>
       <c r="E31">
-        <v>3.61699999999999</v>
+        <v>7.689999999999998</v>
       </c>
       <c r="F31">
-        <v>118.117</v>
+        <v>122.19</v>
       </c>
       <c r="G31">
         <v>55.7</v>
@@ -3823,28 +3823,28 @@
         <v>33.2</v>
       </c>
       <c r="M31">
-        <v>6.5318701</v>
+        <v>6.757107</v>
       </c>
       <c r="N31">
-        <v>26.6681299</v>
+        <v>26.442893</v>
       </c>
       <c r="O31">
-        <v>4.800263382000001</v>
+        <v>4.75972074</v>
       </c>
       <c r="P31">
-        <v>21.867866518</v>
+        <v>21.68317226</v>
       </c>
       <c r="Q31">
-        <v>47.667866518</v>
+        <v>47.48317226</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1264850357903379</v>
+        <v>0.1274822583711729</v>
       </c>
       <c r="T31">
-        <v>1.360465617291028</v>
+        <v>1.377280222635414</v>
       </c>
       <c r="U31">
         <v>0.0553</v>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>5.082771012240431</v>
+        <v>4.913345311832416</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3869,22 +3869,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.102841380859821</v>
+        <v>0.1027280463085021</v>
       </c>
       <c r="C32">
-        <v>298.3264985661175</v>
+        <v>294.9797893289281</v>
       </c>
       <c r="D32">
-        <v>364.8164985661175</v>
+        <v>365.5427893289281</v>
       </c>
       <c r="E32">
-        <v>7.689999999999998</v>
+        <v>11.76300000000001</v>
       </c>
       <c r="F32">
-        <v>122.19</v>
+        <v>126.263</v>
       </c>
       <c r="G32">
         <v>55.7</v>
@@ -3905,28 +3905,28 @@
         <v>33.2</v>
       </c>
       <c r="M32">
-        <v>6.757107</v>
+        <v>6.982343900000001</v>
       </c>
       <c r="N32">
-        <v>26.442893</v>
+        <v>26.2176561</v>
       </c>
       <c r="O32">
-        <v>4.75972074</v>
+        <v>4.719178098</v>
       </c>
       <c r="P32">
-        <v>21.68317226</v>
+        <v>21.498478002</v>
       </c>
       <c r="Q32">
-        <v>47.48317226</v>
+        <v>47.298478002</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1274822583711729</v>
+        <v>0.1285083859543509</v>
       </c>
       <c r="T32">
-        <v>1.377280222635414</v>
+        <v>1.394582207844855</v>
       </c>
       <c r="U32">
         <v>0.0553</v>
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>4.913345311832416</v>
+        <v>4.754850301773306</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3951,22 +3951,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1027280463085021</v>
+        <v>0.1026147117571832</v>
       </c>
       <c r="C33">
-        <v>294.9797893289281</v>
+        <v>291.6359777157936</v>
       </c>
       <c r="D33">
-        <v>365.5427893289281</v>
+        <v>366.2719777157936</v>
       </c>
       <c r="E33">
-        <v>11.76300000000001</v>
+        <v>15.83600000000001</v>
       </c>
       <c r="F33">
-        <v>126.263</v>
+        <v>130.336</v>
       </c>
       <c r="G33">
         <v>55.7</v>
@@ -3987,28 +3987,28 @@
         <v>33.2</v>
       </c>
       <c r="M33">
-        <v>6.982343900000001</v>
+        <v>7.207580800000001</v>
       </c>
       <c r="N33">
-        <v>26.2176561</v>
+        <v>25.9924192</v>
       </c>
       <c r="O33">
-        <v>4.719178098</v>
+        <v>4.678635456</v>
       </c>
       <c r="P33">
-        <v>21.498478002</v>
+        <v>21.313783744</v>
       </c>
       <c r="Q33">
-        <v>47.298478002</v>
+        <v>47.113783744</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1285083859543509</v>
+        <v>0.1295646937605636</v>
       </c>
       <c r="T33">
-        <v>1.394582207844855</v>
+        <v>1.412393074972221</v>
       </c>
       <c r="U33">
         <v>0.0553</v>
@@ -4025,7 +4025,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>4.754850301773306</v>
+        <v>4.60626122984289</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4033,22 +4033,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1026147117571832</v>
+        <v>0.1031778772058643</v>
       </c>
       <c r="C34">
-        <v>291.6359777157936</v>
+        <v>283.9680081436438</v>
       </c>
       <c r="D34">
-        <v>366.2719777157936</v>
+        <v>362.6770081436438</v>
       </c>
       <c r="E34">
-        <v>15.83600000000001</v>
+        <v>19.90900000000002</v>
       </c>
       <c r="F34">
-        <v>130.336</v>
+        <v>134.409</v>
       </c>
       <c r="G34">
         <v>55.7</v>
@@ -4069,45 +4069,45 @@
         <v>33.2</v>
       </c>
       <c r="M34">
-        <v>7.207580800000001</v>
+        <v>7.768840200000001</v>
       </c>
       <c r="N34">
-        <v>25.9924192</v>
+        <v>25.4311598</v>
       </c>
       <c r="O34">
-        <v>4.678635456</v>
+        <v>4.577608764000001</v>
       </c>
       <c r="P34">
-        <v>21.313783744</v>
+        <v>20.853551036</v>
       </c>
       <c r="Q34">
-        <v>47.113783744</v>
+        <v>46.653551036</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1295646937605636</v>
+        <v>0.1306525331430811</v>
       </c>
       <c r="T34">
-        <v>1.412393074972221</v>
+        <v>1.43073560977503</v>
       </c>
       <c r="U34">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V34">
         <v>0.18</v>
       </c>
       <c r="W34">
-        <v>0.045346</v>
+        <v>0.04739600000000001</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y34">
-        <v>4.60626122984289</v>
+        <v>4.273482160181387</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4115,22 +4115,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1031778772058643</v>
+        <v>0.1030850426545454</v>
       </c>
       <c r="C35">
-        <v>283.9680081436438</v>
+        <v>280.4827524441541</v>
       </c>
       <c r="D35">
-        <v>362.6770081436438</v>
+        <v>363.2647524441542</v>
       </c>
       <c r="E35">
-        <v>19.90900000000002</v>
+        <v>23.98200000000003</v>
       </c>
       <c r="F35">
-        <v>134.409</v>
+        <v>138.482</v>
       </c>
       <c r="G35">
         <v>55.7</v>
@@ -4151,28 +4151,28 @@
         <v>33.2</v>
       </c>
       <c r="M35">
-        <v>7.768840200000001</v>
+        <v>8.004259600000003</v>
       </c>
       <c r="N35">
-        <v>25.4311598</v>
+        <v>25.1957404</v>
       </c>
       <c r="O35">
-        <v>4.577608764000001</v>
+        <v>4.535233271999999</v>
       </c>
       <c r="P35">
-        <v>20.853551036</v>
+        <v>20.660507128</v>
       </c>
       <c r="Q35">
-        <v>46.653551036</v>
+        <v>46.460507128</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1306525331430811</v>
+        <v>0.1317733373553719</v>
       </c>
       <c r="T35">
-        <v>1.43073560977503</v>
+        <v>1.449633978965803</v>
       </c>
       <c r="U35">
         <v>0.0578</v>
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>4.273482160181387</v>
+        <v>4.147791508411345</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4197,22 +4197,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1030850426545454</v>
+        <v>0.1029922081032266</v>
       </c>
       <c r="C36">
-        <v>280.4827524441541</v>
+        <v>276.999404801032</v>
       </c>
       <c r="D36">
-        <v>363.2647524441542</v>
+        <v>363.854404801032</v>
       </c>
       <c r="E36">
-        <v>23.98200000000003</v>
+        <v>28.05500000000001</v>
       </c>
       <c r="F36">
-        <v>138.482</v>
+        <v>142.555</v>
       </c>
       <c r="G36">
         <v>55.7</v>
@@ -4233,28 +4233,28 @@
         <v>33.2</v>
       </c>
       <c r="M36">
-        <v>8.004259600000003</v>
+        <v>8.239679000000001</v>
       </c>
       <c r="N36">
-        <v>25.1957404</v>
+        <v>24.960321</v>
       </c>
       <c r="O36">
-        <v>4.535233271999999</v>
+        <v>4.49285778</v>
       </c>
       <c r="P36">
-        <v>20.660507128</v>
+        <v>20.46746322</v>
       </c>
       <c r="Q36">
-        <v>46.460507128</v>
+        <v>46.26746322</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1317733373553719</v>
+        <v>0.1329286278511178</v>
       </c>
       <c r="T36">
-        <v>1.449633978965803</v>
+        <v>1.46911383643937</v>
       </c>
       <c r="U36">
         <v>0.0578</v>
@@ -4271,7 +4271,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>4.147791508411345</v>
+        <v>4.029283179599593</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4279,22 +4279,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1029922081032266</v>
+        <v>0.1039325735519076</v>
       </c>
       <c r="C37">
-        <v>276.999404801032</v>
+        <v>267.0406149637766</v>
       </c>
       <c r="D37">
-        <v>363.854404801032</v>
+        <v>357.9686149637767</v>
       </c>
       <c r="E37">
-        <v>28.05500000000001</v>
+        <v>32.12800000000001</v>
       </c>
       <c r="F37">
-        <v>142.555</v>
+        <v>146.628</v>
       </c>
       <c r="G37">
         <v>55.7</v>
@@ -4315,45 +4315,45 @@
         <v>33.2</v>
       </c>
       <c r="M37">
-        <v>8.239679000000001</v>
+        <v>8.988296400000001</v>
       </c>
       <c r="N37">
-        <v>24.960321</v>
+        <v>24.2117036</v>
       </c>
       <c r="O37">
-        <v>4.49285778</v>
+        <v>4.358106648</v>
       </c>
       <c r="P37">
-        <v>20.46746322</v>
+        <v>19.853596952</v>
       </c>
       <c r="Q37">
-        <v>46.26746322</v>
+        <v>45.653596952</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1329286278511178</v>
+        <v>0.1341200211748557</v>
       </c>
       <c r="T37">
-        <v>1.46911383643937</v>
+        <v>1.489202439458985</v>
       </c>
       <c r="U37">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V37">
         <v>0.18</v>
       </c>
       <c r="W37">
-        <v>0.04739600000000001</v>
+        <v>0.05026600000000001</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y37">
-        <v>4.029283179599593</v>
+        <v>3.693692166181791</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4361,22 +4361,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1039325735519077</v>
+        <v>0.1038684390005888</v>
       </c>
       <c r="C38">
-        <v>267.0406149637766</v>
+        <v>263.3629787259525</v>
       </c>
       <c r="D38">
-        <v>357.9686149637766</v>
+        <v>358.3639787259525</v>
       </c>
       <c r="E38">
-        <v>32.12799999999999</v>
+        <v>36.20099999999999</v>
       </c>
       <c r="F38">
-        <v>146.628</v>
+        <v>150.701</v>
       </c>
       <c r="G38">
         <v>55.7</v>
@@ -4397,28 +4397,28 @@
         <v>33.2</v>
       </c>
       <c r="M38">
-        <v>8.988296399999999</v>
+        <v>9.2379713</v>
       </c>
       <c r="N38">
-        <v>24.2117036</v>
+        <v>23.9620287</v>
       </c>
       <c r="O38">
-        <v>4.358106648000001</v>
+        <v>4.313165166000001</v>
       </c>
       <c r="P38">
-        <v>19.853596952</v>
+        <v>19.648863534</v>
       </c>
       <c r="Q38">
-        <v>45.653596952</v>
+        <v>45.448863534</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1341200211748557</v>
+        <v>0.135349236508871</v>
       </c>
       <c r="T38">
-        <v>1.489202439458985</v>
+        <v>1.509928775907794</v>
       </c>
       <c r="U38">
         <v>0.0613</v>
@@ -4435,7 +4435,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>3.693692166181792</v>
+        <v>3.593862648176879</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4443,22 +4443,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1038684390005888</v>
+        <v>0.1046767844492699</v>
       </c>
       <c r="C39">
-        <v>263.3629787259525</v>
+        <v>254.3698409520566</v>
       </c>
       <c r="D39">
-        <v>358.3639787259525</v>
+        <v>353.4438409520566</v>
       </c>
       <c r="E39">
-        <v>36.20099999999999</v>
+        <v>40.274</v>
       </c>
       <c r="F39">
-        <v>150.701</v>
+        <v>154.774</v>
       </c>
       <c r="G39">
         <v>55.7</v>
@@ -4479,45 +4479,45 @@
         <v>33.2</v>
       </c>
       <c r="M39">
-        <v>9.2379713</v>
+        <v>9.921013400000001</v>
       </c>
       <c r="N39">
-        <v>23.9620287</v>
+        <v>23.2789866</v>
       </c>
       <c r="O39">
-        <v>4.313165166000001</v>
+        <v>4.190217588</v>
       </c>
       <c r="P39">
-        <v>19.648863534</v>
+        <v>19.088769012</v>
       </c>
       <c r="Q39">
-        <v>45.448863534</v>
+        <v>44.888769012</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.135349236508871</v>
+        <v>0.1366181039504352</v>
       </c>
       <c r="T39">
-        <v>1.509928775907794</v>
+        <v>1.531323703854952</v>
       </c>
       <c r="U39">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V39">
         <v>0.18</v>
       </c>
       <c r="W39">
-        <v>0.05026600000000001</v>
+        <v>0.052562</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y39">
-        <v>3.593862648176879</v>
+        <v>3.346432331197133</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1046767844492699</v>
+        <v>0.104635609897951</v>
       </c>
       <c r="C40">
-        <v>254.3698409520566</v>
+        <v>250.5441893112029</v>
       </c>
       <c r="D40">
-        <v>353.4438409520566</v>
+        <v>353.6911893112029</v>
       </c>
       <c r="E40">
-        <v>40.274</v>
+        <v>44.34700000000001</v>
       </c>
       <c r="F40">
-        <v>154.774</v>
+        <v>158.847</v>
       </c>
       <c r="G40">
         <v>55.7</v>
@@ -4561,28 +4561,28 @@
         <v>33.2</v>
       </c>
       <c r="M40">
-        <v>9.921013400000001</v>
+        <v>10.1820927</v>
       </c>
       <c r="N40">
-        <v>23.2789866</v>
+        <v>23.0179073</v>
       </c>
       <c r="O40">
-        <v>4.190217588</v>
+        <v>4.143223314</v>
       </c>
       <c r="P40">
-        <v>19.088769012</v>
+        <v>18.874683986</v>
       </c>
       <c r="Q40">
-        <v>44.888769012</v>
+        <v>44.67468398600001</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1366181039504352</v>
+        <v>0.1379285736031983</v>
       </c>
       <c r="T40">
-        <v>1.531323703854952</v>
+        <v>1.553420104849558</v>
       </c>
       <c r="U40">
         <v>0.0641</v>
@@ -4599,7 +4599,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>3.346432331197133</v>
+        <v>3.26062637398695</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4607,22 +4607,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.104635609897951</v>
+        <v>0.104594435346632</v>
       </c>
       <c r="C41">
-        <v>250.5441893112029</v>
+        <v>246.7188841132617</v>
       </c>
       <c r="D41">
-        <v>353.6911893112029</v>
+        <v>353.9388841132617</v>
       </c>
       <c r="E41">
-        <v>44.34700000000001</v>
+        <v>48.42000000000002</v>
       </c>
       <c r="F41">
-        <v>158.847</v>
+        <v>162.92</v>
       </c>
       <c r="G41">
         <v>55.7</v>
@@ -4643,28 +4643,28 @@
         <v>33.2</v>
       </c>
       <c r="M41">
-        <v>10.1820927</v>
+        <v>10.443172</v>
       </c>
       <c r="N41">
-        <v>23.0179073</v>
+        <v>22.756828</v>
       </c>
       <c r="O41">
-        <v>4.143223314</v>
+        <v>4.09622904</v>
       </c>
       <c r="P41">
-        <v>18.874683986</v>
+        <v>18.66059896</v>
       </c>
       <c r="Q41">
-        <v>44.67468398600001</v>
+        <v>44.46059896</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1379285736031983</v>
+        <v>0.1392827255777201</v>
       </c>
       <c r="T41">
-        <v>1.553420104849558</v>
+        <v>1.576253052543984</v>
       </c>
       <c r="U41">
         <v>0.0641</v>
@@ -4681,7 +4681,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>3.26062637398695</v>
+        <v>3.179110714637276</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4689,22 +4689,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.104594435346632</v>
+        <v>0.1045532607953132</v>
       </c>
       <c r="C42">
-        <v>246.7188841132617</v>
+        <v>242.893926086599</v>
       </c>
       <c r="D42">
-        <v>353.9388841132617</v>
+        <v>354.186926086599</v>
       </c>
       <c r="E42">
-        <v>48.42000000000002</v>
+        <v>52.49300000000002</v>
       </c>
       <c r="F42">
-        <v>162.92</v>
+        <v>166.993</v>
       </c>
       <c r="G42">
         <v>55.7</v>
@@ -4725,28 +4725,28 @@
         <v>33.2</v>
       </c>
       <c r="M42">
-        <v>10.443172</v>
+        <v>10.7042513</v>
       </c>
       <c r="N42">
-        <v>22.756828</v>
+        <v>22.4957487</v>
       </c>
       <c r="O42">
-        <v>4.09622904</v>
+        <v>4.049234766</v>
       </c>
       <c r="P42">
-        <v>18.66059896</v>
+        <v>18.446513934</v>
       </c>
       <c r="Q42">
-        <v>44.46059896</v>
+        <v>44.24651393400001</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1392827255777201</v>
+        <v>0.1406827810090054</v>
       </c>
       <c r="T42">
-        <v>1.576253052543984</v>
+        <v>1.599859998465339</v>
       </c>
       <c r="U42">
         <v>0.0641</v>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>3.179110714637276</v>
+        <v>3.101571428914416</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4771,22 +4771,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1045532607953132</v>
+        <v>0.1045120862439943</v>
       </c>
       <c r="C43">
-        <v>242.893926086599</v>
+        <v>239.0693159616246</v>
       </c>
       <c r="D43">
-        <v>354.186926086599</v>
+        <v>354.4353159616246</v>
       </c>
       <c r="E43">
-        <v>52.49300000000002</v>
+        <v>56.56600000000003</v>
       </c>
       <c r="F43">
-        <v>166.993</v>
+        <v>171.066</v>
       </c>
       <c r="G43">
         <v>55.7</v>
@@ -4807,28 +4807,28 @@
         <v>33.2</v>
       </c>
       <c r="M43">
-        <v>10.7042513</v>
+        <v>10.9653306</v>
       </c>
       <c r="N43">
-        <v>22.4957487</v>
+        <v>22.2346694</v>
       </c>
       <c r="O43">
-        <v>4.049234766</v>
+        <v>4.002240492</v>
       </c>
       <c r="P43">
-        <v>18.446513934</v>
+        <v>18.232428908</v>
       </c>
       <c r="Q43">
-        <v>44.24651393400001</v>
+        <v>44.032428908</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1406827810090054</v>
+        <v>0.1421311142137832</v>
       </c>
       <c r="T43">
-        <v>1.599859998465339</v>
+        <v>1.624280977004673</v>
       </c>
       <c r="U43">
         <v>0.0641</v>
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>3.101571428914416</v>
+        <v>3.027724490130739</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4853,22 +4853,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1045120862439943</v>
+        <v>0.1072211916926754</v>
       </c>
       <c r="C44">
-        <v>239.0693159616244</v>
+        <v>219.3632320175507</v>
       </c>
       <c r="D44">
-        <v>354.4353159616244</v>
+        <v>338.8022320175507</v>
       </c>
       <c r="E44">
-        <v>56.566</v>
+        <v>60.63900000000001</v>
       </c>
       <c r="F44">
-        <v>171.066</v>
+        <v>175.139</v>
       </c>
       <c r="G44">
         <v>55.7</v>
@@ -4889,45 +4889,45 @@
         <v>33.2</v>
       </c>
       <c r="M44">
-        <v>10.9653306</v>
+        <v>12.5924941</v>
       </c>
       <c r="N44">
-        <v>22.2346694</v>
+        <v>20.6075059</v>
       </c>
       <c r="O44">
-        <v>4.002240492</v>
+        <v>3.709351062</v>
       </c>
       <c r="P44">
-        <v>18.232428908</v>
+        <v>16.898154838</v>
       </c>
       <c r="Q44">
-        <v>44.032428908</v>
+        <v>42.698154838</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1421311142137832</v>
+        <v>0.1436302661275006</v>
       </c>
       <c r="T44">
-        <v>1.624280977004673</v>
+        <v>1.649558831983983</v>
       </c>
       <c r="U44">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V44">
         <v>0.18</v>
       </c>
       <c r="W44">
-        <v>0.052562</v>
+        <v>0.05895800000000001</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y44">
-        <v>3.02772449013074</v>
+        <v>2.636491209473745</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4935,22 +4935,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1072211916926754</v>
+        <v>0.1072439771413565</v>
       </c>
       <c r="C45">
-        <v>219.3632320175507</v>
+        <v>215.1645930008424</v>
       </c>
       <c r="D45">
-        <v>338.8022320175507</v>
+        <v>338.6765930008424</v>
       </c>
       <c r="E45">
-        <v>60.63900000000001</v>
+        <v>64.71200000000002</v>
       </c>
       <c r="F45">
-        <v>175.139</v>
+        <v>179.212</v>
       </c>
       <c r="G45">
         <v>55.7</v>
@@ -4971,28 +4971,28 @@
         <v>33.2</v>
       </c>
       <c r="M45">
-        <v>12.5924941</v>
+        <v>12.8853428</v>
       </c>
       <c r="N45">
-        <v>20.6075059</v>
+        <v>20.3146572</v>
       </c>
       <c r="O45">
-        <v>3.709351062</v>
+        <v>3.656638296</v>
       </c>
       <c r="P45">
-        <v>16.898154838</v>
+        <v>16.658018904</v>
       </c>
       <c r="Q45">
-        <v>42.698154838</v>
+        <v>42.458018904</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1436302661275006</v>
+        <v>0.1451829591809937</v>
       </c>
       <c r="T45">
-        <v>1.649558831983983</v>
+        <v>1.675739467498269</v>
       </c>
       <c r="U45">
         <v>0.07190000000000001</v>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>2.636491209473745</v>
+        <v>2.576570954712978</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5017,22 +5017,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1072439771413565</v>
+        <v>0.1072667625900376</v>
       </c>
       <c r="C46">
-        <v>215.1645930008424</v>
+        <v>210.9660471317559</v>
       </c>
       <c r="D46">
-        <v>338.6765930008424</v>
+        <v>338.5510471317559</v>
       </c>
       <c r="E46">
-        <v>64.71200000000002</v>
+        <v>68.785</v>
       </c>
       <c r="F46">
-        <v>179.212</v>
+        <v>183.285</v>
       </c>
       <c r="G46">
         <v>55.7</v>
@@ -5053,28 +5053,28 @@
         <v>33.2</v>
       </c>
       <c r="M46">
-        <v>12.8853428</v>
+        <v>13.1781915</v>
       </c>
       <c r="N46">
-        <v>20.3146572</v>
+        <v>20.0218085</v>
       </c>
       <c r="O46">
-        <v>3.656638296</v>
+        <v>3.60392553</v>
       </c>
       <c r="P46">
-        <v>16.658018904</v>
+        <v>16.41788297</v>
       </c>
       <c r="Q46">
-        <v>42.458018904</v>
+        <v>42.21788297000001</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1451829591809937</v>
+        <v>0.1467921138000683</v>
       </c>
       <c r="T46">
-        <v>1.675739467498269</v>
+        <v>1.702872126122164</v>
       </c>
       <c r="U46">
         <v>0.07190000000000001</v>
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>2.576570954712978</v>
+        <v>2.519313822386023</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5099,22 +5099,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1072667625900376</v>
+        <v>0.1087606280387187</v>
       </c>
       <c r="C47">
-        <v>210.9660471317559</v>
+        <v>198.8602538182279</v>
       </c>
       <c r="D47">
-        <v>338.5510471317559</v>
+        <v>330.5182538182279</v>
       </c>
       <c r="E47">
-        <v>68.785</v>
+        <v>72.858</v>
       </c>
       <c r="F47">
-        <v>183.285</v>
+        <v>187.358</v>
       </c>
       <c r="G47">
         <v>55.7</v>
@@ -5135,45 +5135,45 @@
         <v>33.2</v>
       </c>
       <c r="M47">
-        <v>13.1781915</v>
+        <v>14.2017364</v>
       </c>
       <c r="N47">
-        <v>20.0218085</v>
+        <v>18.9982636</v>
       </c>
       <c r="O47">
-        <v>3.60392553</v>
+        <v>3.419687448</v>
       </c>
       <c r="P47">
-        <v>16.41788297</v>
+        <v>15.578576152</v>
       </c>
       <c r="Q47">
-        <v>42.21788297000001</v>
+        <v>41.378576152</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1467921138000683</v>
+        <v>0.1484608667383679</v>
       </c>
       <c r="T47">
-        <v>1.702872126122164</v>
+        <v>1.731009698028427</v>
       </c>
       <c r="U47">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V47">
         <v>0.18</v>
       </c>
       <c r="W47">
-        <v>0.05895800000000001</v>
+        <v>0.06215600000000001</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y47">
-        <v>2.519313822386023</v>
+        <v>2.337742305933801</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5181,22 +5181,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1087606280387187</v>
+        <v>0.1088153934873998</v>
       </c>
       <c r="C48">
-        <v>198.8602538182279</v>
+        <v>194.5000068541783</v>
       </c>
       <c r="D48">
-        <v>330.5182538182279</v>
+        <v>330.2310068541783</v>
       </c>
       <c r="E48">
-        <v>72.858</v>
+        <v>76.93100000000001</v>
       </c>
       <c r="F48">
-        <v>187.358</v>
+        <v>191.431</v>
       </c>
       <c r="G48">
         <v>55.7</v>
@@ -5217,28 +5217,28 @@
         <v>33.2</v>
       </c>
       <c r="M48">
-        <v>14.2017364</v>
+        <v>14.5104698</v>
       </c>
       <c r="N48">
-        <v>18.9982636</v>
+        <v>18.6895302</v>
       </c>
       <c r="O48">
-        <v>3.419687448</v>
+        <v>3.364115436</v>
       </c>
       <c r="P48">
-        <v>15.578576152</v>
+        <v>15.325414764</v>
       </c>
       <c r="Q48">
-        <v>41.378576152</v>
+        <v>41.125414764</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1484608667383679</v>
+        <v>0.1501925914856599</v>
       </c>
       <c r="T48">
-        <v>1.731009698028427</v>
+        <v>1.760209065100963</v>
       </c>
       <c r="U48">
         <v>0.07580000000000001</v>
@@ -5255,7 +5255,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>2.337742305933801</v>
+        <v>2.288003107935209</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5263,22 +5263,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1088153934873998</v>
+        <v>0.1088701589360809</v>
       </c>
       <c r="C49">
-        <v>194.5000068541783</v>
+        <v>190.1402587380508</v>
       </c>
       <c r="D49">
-        <v>330.2310068541783</v>
+        <v>329.9442587380508</v>
       </c>
       <c r="E49">
-        <v>76.93100000000001</v>
+        <v>81.00400000000002</v>
       </c>
       <c r="F49">
-        <v>191.431</v>
+        <v>195.504</v>
       </c>
       <c r="G49">
         <v>55.7</v>
@@ -5299,28 +5299,28 @@
         <v>33.2</v>
       </c>
       <c r="M49">
-        <v>14.5104698</v>
+        <v>14.8192032</v>
       </c>
       <c r="N49">
-        <v>18.6895302</v>
+        <v>18.3807968</v>
       </c>
       <c r="O49">
-        <v>3.364115436</v>
+        <v>3.308543424</v>
       </c>
       <c r="P49">
-        <v>15.325414764</v>
+        <v>15.072253376</v>
       </c>
       <c r="Q49">
-        <v>41.125414764</v>
+        <v>40.872253376</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1501925914856599</v>
+        <v>0.1519909210309248</v>
       </c>
       <c r="T49">
-        <v>1.760209065100963</v>
+        <v>1.790531484753213</v>
       </c>
       <c r="U49">
         <v>0.07580000000000001</v>
@@ -5337,7 +5337,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>2.288003107935209</v>
+        <v>2.240336376519893</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5345,22 +5345,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1088701589360809</v>
+        <v>0.108924924384762</v>
       </c>
       <c r="C50">
-        <v>190.1402587380508</v>
+        <v>185.7810081714853</v>
       </c>
       <c r="D50">
-        <v>329.9442587380508</v>
+        <v>329.6580081714853</v>
       </c>
       <c r="E50">
-        <v>81.00399999999999</v>
+        <v>85.077</v>
       </c>
       <c r="F50">
-        <v>195.504</v>
+        <v>199.577</v>
       </c>
       <c r="G50">
         <v>55.7</v>
@@ -5381,28 +5381,28 @@
         <v>33.2</v>
       </c>
       <c r="M50">
-        <v>14.8192032</v>
+        <v>15.1279366</v>
       </c>
       <c r="N50">
-        <v>18.3807968</v>
+        <v>18.0720634</v>
       </c>
       <c r="O50">
-        <v>3.308543424</v>
+        <v>3.252971412</v>
       </c>
       <c r="P50">
-        <v>15.072253376</v>
+        <v>14.819091988</v>
       </c>
       <c r="Q50">
-        <v>40.872253376</v>
+        <v>40.619091988</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1519909210309247</v>
+        <v>0.1538597733034548</v>
       </c>
       <c r="T50">
-        <v>1.790531484753212</v>
+        <v>1.822043018901628</v>
       </c>
       <c r="U50">
         <v>0.07580000000000001</v>
@@ -5419,7 +5419,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>2.240336376519893</v>
+        <v>2.19461522597867</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5427,22 +5427,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.108924924384762</v>
+        <v>0.1089796898334431</v>
       </c>
       <c r="C51">
-        <v>185.7810081714853</v>
+        <v>181.4222538606233</v>
       </c>
       <c r="D51">
-        <v>329.6580081714853</v>
+        <v>329.3722538606233</v>
       </c>
       <c r="E51">
-        <v>85.077</v>
+        <v>89.15000000000001</v>
       </c>
       <c r="F51">
-        <v>199.577</v>
+        <v>203.65</v>
       </c>
       <c r="G51">
         <v>55.7</v>
@@ -5463,28 +5463,28 @@
         <v>33.2</v>
       </c>
       <c r="M51">
-        <v>15.1279366</v>
+        <v>15.43667</v>
       </c>
       <c r="N51">
-        <v>18.0720634</v>
+        <v>17.76333</v>
       </c>
       <c r="O51">
-        <v>3.252971412</v>
+        <v>3.197399400000001</v>
       </c>
       <c r="P51">
-        <v>14.819091988</v>
+        <v>14.5659306</v>
       </c>
       <c r="Q51">
-        <v>40.619091988</v>
+        <v>40.36593060000001</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1538597733034548</v>
+        <v>0.1558033796668861</v>
       </c>
       <c r="T51">
-        <v>1.822043018901628</v>
+        <v>1.854815014415981</v>
       </c>
       <c r="U51">
         <v>0.07580000000000001</v>
@@ -5501,7 +5501,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>2.19461522597867</v>
+        <v>2.150722921459097</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5509,22 +5509,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1089796898334431</v>
+        <v>0.1090344552821242</v>
       </c>
       <c r="C52">
-        <v>181.4222538606233</v>
+        <v>177.0639945160887</v>
       </c>
       <c r="D52">
-        <v>329.3722538606233</v>
+        <v>329.0869945160887</v>
       </c>
       <c r="E52">
-        <v>89.15000000000001</v>
+        <v>93.22300000000001</v>
       </c>
       <c r="F52">
-        <v>203.65</v>
+        <v>207.723</v>
       </c>
       <c r="G52">
         <v>55.7</v>
@@ -5545,28 +5545,28 @@
         <v>33.2</v>
       </c>
       <c r="M52">
-        <v>15.43667</v>
+        <v>15.7454034</v>
       </c>
       <c r="N52">
-        <v>17.76333</v>
+        <v>17.4545966</v>
       </c>
       <c r="O52">
-        <v>3.197399400000001</v>
+        <v>3.141827388</v>
       </c>
       <c r="P52">
-        <v>14.5659306</v>
+        <v>14.312769212</v>
       </c>
       <c r="Q52">
-        <v>40.36593060000001</v>
+        <v>40.112769212</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1558033796668861</v>
+        <v>0.1578263169022943</v>
       </c>
       <c r="T52">
-        <v>1.854815014415981</v>
+        <v>1.888924642400307</v>
       </c>
       <c r="U52">
         <v>0.07580000000000001</v>
@@ -5583,7 +5583,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>2.150722921459097</v>
+        <v>2.108551883783429</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1090344552821242</v>
+        <v>0.1090892207308053</v>
       </c>
       <c r="C53">
-        <v>177.0639945160887</v>
+        <v>172.7062288529682</v>
       </c>
       <c r="D53">
-        <v>329.0869945160887</v>
+        <v>328.8022288529683</v>
       </c>
       <c r="E53">
-        <v>93.22300000000001</v>
+        <v>97.29600000000002</v>
       </c>
       <c r="F53">
-        <v>207.723</v>
+        <v>211.796</v>
       </c>
       <c r="G53">
         <v>55.7</v>
@@ -5627,28 +5627,28 @@
         <v>33.2</v>
       </c>
       <c r="M53">
-        <v>15.7454034</v>
+        <v>16.0541368</v>
       </c>
       <c r="N53">
-        <v>17.4545966</v>
+        <v>17.1458632</v>
       </c>
       <c r="O53">
-        <v>3.141827388</v>
+        <v>3.086255376</v>
       </c>
       <c r="P53">
-        <v>14.312769212</v>
+        <v>14.059607824</v>
       </c>
       <c r="Q53">
-        <v>40.112769212</v>
+        <v>39.859607824</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1578263169022943</v>
+        <v>0.1599335431891777</v>
       </c>
       <c r="T53">
-        <v>1.888924642400307</v>
+        <v>1.92445550488398</v>
       </c>
       <c r="U53">
         <v>0.07580000000000001</v>
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>2.108551883783429</v>
+        <v>2.068002809095286</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5673,22 +5673,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1090892207308053</v>
+        <v>0.1091439861794864</v>
       </c>
       <c r="C54">
-        <v>172.7062288529682</v>
+        <v>168.3489555907921</v>
       </c>
       <c r="D54">
-        <v>328.8022288529683</v>
+        <v>328.5179555907921</v>
       </c>
       <c r="E54">
-        <v>97.29600000000002</v>
+        <v>101.369</v>
       </c>
       <c r="F54">
-        <v>211.796</v>
+        <v>215.869</v>
       </c>
       <c r="G54">
         <v>55.7</v>
@@ -5709,28 +5709,28 @@
         <v>33.2</v>
       </c>
       <c r="M54">
-        <v>16.0541368</v>
+        <v>16.3628702</v>
       </c>
       <c r="N54">
-        <v>17.1458632</v>
+        <v>16.8371298</v>
       </c>
       <c r="O54">
-        <v>3.086255376</v>
+        <v>3.030683364</v>
       </c>
       <c r="P54">
-        <v>14.059607824</v>
+        <v>13.806446436</v>
       </c>
       <c r="Q54">
-        <v>39.859607824</v>
+        <v>39.606446436</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1599335431891777</v>
+        <v>0.1621304386797583</v>
       </c>
       <c r="T54">
-        <v>1.92445550488398</v>
+        <v>1.961498318962704</v>
       </c>
       <c r="U54">
         <v>0.07580000000000001</v>
@@ -5747,7 +5747,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>2.068002809095286</v>
+        <v>2.028983888168959</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5755,22 +5755,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1091439861794864</v>
+        <v>0.1154865116281675</v>
       </c>
       <c r="C55">
-        <v>168.3489555907921</v>
+        <v>134.3758580683173</v>
       </c>
       <c r="D55">
-        <v>328.5179555907921</v>
+        <v>298.6178580683173</v>
       </c>
       <c r="E55">
-        <v>101.369</v>
+        <v>105.442</v>
       </c>
       <c r="F55">
-        <v>215.869</v>
+        <v>219.942</v>
       </c>
       <c r="G55">
         <v>55.7</v>
@@ -5791,45 +5791,45 @@
         <v>33.2</v>
       </c>
       <c r="M55">
-        <v>16.3628702</v>
+        <v>19.79478</v>
       </c>
       <c r="N55">
-        <v>16.8371298</v>
+        <v>13.40522</v>
       </c>
       <c r="O55">
-        <v>3.030683364</v>
+        <v>2.412939600000001</v>
       </c>
       <c r="P55">
-        <v>13.806446436</v>
+        <v>10.9922804</v>
       </c>
       <c r="Q55">
-        <v>39.606446436</v>
+        <v>36.7922804</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1621304386797583</v>
+        <v>0.1644228513655815</v>
       </c>
       <c r="T55">
-        <v>1.961498318962704</v>
+        <v>2.000151690175284</v>
       </c>
       <c r="U55">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V55">
         <v>0.18</v>
       </c>
       <c r="W55">
-        <v>0.06215600000000001</v>
+        <v>0.0738</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y55">
-        <v>2.028983888168959</v>
+        <v>1.677209850273658</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5837,22 +5837,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1154865116281675</v>
+        <v>0.1156577170768486</v>
       </c>
       <c r="C56">
-        <v>134.3758580683173</v>
+        <v>129.5710133056473</v>
       </c>
       <c r="D56">
-        <v>298.6178580683173</v>
+        <v>297.8860133056473</v>
       </c>
       <c r="E56">
-        <v>105.442</v>
+        <v>109.515</v>
       </c>
       <c r="F56">
-        <v>219.942</v>
+        <v>224.015</v>
       </c>
       <c r="G56">
         <v>55.7</v>
@@ -5873,28 +5873,28 @@
         <v>33.2</v>
       </c>
       <c r="M56">
-        <v>19.79478</v>
+        <v>20.16135</v>
       </c>
       <c r="N56">
-        <v>13.40522</v>
+        <v>13.03865</v>
       </c>
       <c r="O56">
-        <v>2.412939600000001</v>
+        <v>2.346957</v>
       </c>
       <c r="P56">
-        <v>10.9922804</v>
+        <v>10.691693</v>
       </c>
       <c r="Q56">
-        <v>36.7922804</v>
+        <v>36.491693</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1644228513655815</v>
+        <v>0.1668171490596635</v>
       </c>
       <c r="T56">
-        <v>2.000151690175284</v>
+        <v>2.040522988997313</v>
       </c>
       <c r="U56">
         <v>0.09</v>
@@ -5911,7 +5911,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>1.677209850273658</v>
+        <v>1.646715125723228</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5919,22 +5919,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1156577170768486</v>
+        <v>0.1158289225255297</v>
       </c>
       <c r="C57">
-        <v>129.5710133056473</v>
+        <v>124.76974694477</v>
       </c>
       <c r="D57">
-        <v>297.8860133056473</v>
+        <v>297.1577469447701</v>
       </c>
       <c r="E57">
-        <v>109.515</v>
+        <v>113.588</v>
       </c>
       <c r="F57">
-        <v>224.015</v>
+        <v>228.088</v>
       </c>
       <c r="G57">
         <v>55.7</v>
@@ -5955,28 +5955,28 @@
         <v>33.2</v>
       </c>
       <c r="M57">
-        <v>20.16135</v>
+        <v>20.52792</v>
       </c>
       <c r="N57">
-        <v>13.03865</v>
+        <v>12.67208</v>
       </c>
       <c r="O57">
-        <v>2.346957</v>
+        <v>2.2809744</v>
       </c>
       <c r="P57">
-        <v>10.691693</v>
+        <v>10.3911056</v>
       </c>
       <c r="Q57">
-        <v>36.491693</v>
+        <v>36.1911056</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1668171490596635</v>
+        <v>0.1693202784671129</v>
       </c>
       <c r="T57">
-        <v>2.040522988997313</v>
+        <v>2.082729346856706</v>
       </c>
       <c r="U57">
         <v>0.09</v>
@@ -5993,7 +5993,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>1.646715125723228</v>
+        <v>1.61730949847817</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6001,22 +6001,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1158289225255297</v>
+        <v>0.1160001279742108</v>
       </c>
       <c r="C58">
-        <v>124.76974694477</v>
+        <v>119.9720328044563</v>
       </c>
       <c r="D58">
-        <v>297.1577469447701</v>
+        <v>296.4330328044563</v>
       </c>
       <c r="E58">
-        <v>113.588</v>
+        <v>117.661</v>
       </c>
       <c r="F58">
-        <v>228.088</v>
+        <v>232.161</v>
       </c>
       <c r="G58">
         <v>55.7</v>
@@ -6037,28 +6037,28 @@
         <v>33.2</v>
       </c>
       <c r="M58">
-        <v>20.52792</v>
+        <v>20.89449</v>
       </c>
       <c r="N58">
-        <v>12.67208</v>
+        <v>12.30551</v>
       </c>
       <c r="O58">
-        <v>2.2809744</v>
+        <v>2.2149918</v>
       </c>
       <c r="P58">
-        <v>10.3911056</v>
+        <v>10.0905182</v>
       </c>
       <c r="Q58">
-        <v>36.1911056</v>
+        <v>35.8905182</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1693202784671129</v>
+        <v>0.1719398324981646</v>
       </c>
       <c r="T58">
-        <v>2.082729346856706</v>
+        <v>2.126898791128164</v>
       </c>
       <c r="U58">
         <v>0.09</v>
@@ -6075,7 +6075,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>1.61730949847817</v>
+        <v>1.588935647627676</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6083,22 +6083,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1160001279742108</v>
+        <v>0.1161713334228919</v>
       </c>
       <c r="C59">
-        <v>119.9720328044563</v>
+        <v>115.1778449582604</v>
       </c>
       <c r="D59">
-        <v>296.4330328044563</v>
+        <v>295.7118449582605</v>
       </c>
       <c r="E59">
-        <v>117.661</v>
+        <v>121.734</v>
       </c>
       <c r="F59">
-        <v>232.161</v>
+        <v>236.234</v>
       </c>
       <c r="G59">
         <v>55.7</v>
@@ -6119,28 +6119,28 @@
         <v>33.2</v>
       </c>
       <c r="M59">
-        <v>20.89449</v>
+        <v>21.26106</v>
       </c>
       <c r="N59">
-        <v>12.30551</v>
+        <v>11.93894</v>
       </c>
       <c r="O59">
-        <v>2.2149918</v>
+        <v>2.1490092</v>
       </c>
       <c r="P59">
-        <v>10.0905182</v>
+        <v>9.789930799999999</v>
       </c>
       <c r="Q59">
-        <v>35.8905182</v>
+        <v>35.5899308</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1719398324981646</v>
+        <v>0.1746841271973616</v>
       </c>
       <c r="T59">
-        <v>2.126898791128164</v>
+        <v>2.173171542269692</v>
       </c>
       <c r="U59">
         <v>0.09</v>
@@ -6157,7 +6157,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>1.588935647627676</v>
+        <v>1.561540205427199</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6165,22 +6165,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1161713334228919</v>
+        <v>0.116342538871573</v>
       </c>
       <c r="C60">
-        <v>115.1778449582604</v>
+        <v>110.3871577314289</v>
       </c>
       <c r="D60">
-        <v>295.7118449582604</v>
+        <v>294.9941577314289</v>
       </c>
       <c r="E60">
-        <v>121.734</v>
+        <v>125.807</v>
       </c>
       <c r="F60">
-        <v>236.234</v>
+        <v>240.307</v>
       </c>
       <c r="G60">
         <v>55.7</v>
@@ -6201,28 +6201,28 @@
         <v>33.2</v>
       </c>
       <c r="M60">
-        <v>21.26106</v>
+        <v>21.62763</v>
       </c>
       <c r="N60">
-        <v>11.93894000000001</v>
+        <v>11.57237000000001</v>
       </c>
       <c r="O60">
-        <v>2.149009200000001</v>
+        <v>2.083026600000001</v>
       </c>
       <c r="P60">
-        <v>9.789930800000004</v>
+        <v>9.489343400000006</v>
       </c>
       <c r="Q60">
-        <v>35.5899308</v>
+        <v>35.28934340000001</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1746841271973616</v>
+        <v>0.1775622899306658</v>
       </c>
       <c r="T60">
-        <v>2.173171542269692</v>
+        <v>2.221701500783977</v>
       </c>
       <c r="U60">
         <v>0.09</v>
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>1.561540205427199</v>
+        <v>1.535073422284365</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6247,22 +6247,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.116342538871573</v>
+        <v>0.1165137443202541</v>
       </c>
       <c r="C61">
-        <v>110.3871577314289</v>
+        <v>105.5999456978533</v>
       </c>
       <c r="D61">
-        <v>294.9941577314289</v>
+        <v>294.2799456978533</v>
       </c>
       <c r="E61">
-        <v>125.807</v>
+        <v>129.88</v>
       </c>
       <c r="F61">
-        <v>240.307</v>
+        <v>244.38</v>
       </c>
       <c r="G61">
         <v>55.7</v>
@@ -6283,28 +6283,28 @@
         <v>33.2</v>
       </c>
       <c r="M61">
-        <v>21.62763</v>
+        <v>21.9942</v>
       </c>
       <c r="N61">
-        <v>11.57237000000001</v>
+        <v>11.2058</v>
       </c>
       <c r="O61">
-        <v>2.083026600000001</v>
+        <v>2.017044000000001</v>
       </c>
       <c r="P61">
-        <v>9.489343400000006</v>
+        <v>9.188756000000003</v>
       </c>
       <c r="Q61">
-        <v>35.28934340000001</v>
+        <v>34.988756</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1775622899306658</v>
+        <v>0.1805843608006352</v>
       </c>
       <c r="T61">
-        <v>2.221701500783977</v>
+        <v>2.272657957223977</v>
       </c>
       <c r="U61">
         <v>0.09</v>
@@ -6321,7 +6321,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>1.535073422284365</v>
+        <v>1.509488865246292</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6329,22 +6329,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1165137443202541</v>
+        <v>0.1471382422735887</v>
       </c>
       <c r="C62">
-        <v>105.5999456978533</v>
+        <v>12.59531048751833</v>
       </c>
       <c r="D62">
-        <v>294.2799456978533</v>
+        <v>205.3483104875183</v>
       </c>
       <c r="E62">
-        <v>129.88</v>
+        <v>133.953</v>
       </c>
       <c r="F62">
-        <v>244.38</v>
+        <v>248.453</v>
       </c>
       <c r="G62">
         <v>55.7</v>
@@ -6365,45 +6365,45 @@
         <v>33.2</v>
       </c>
       <c r="M62">
-        <v>21.9942</v>
+        <v>36.4729004</v>
       </c>
       <c r="N62">
-        <v>11.2058</v>
+        <v>-3.272900399999997</v>
       </c>
       <c r="O62">
-        <v>2.017044000000001</v>
+        <v>-0.5891220719999996</v>
       </c>
       <c r="P62">
-        <v>9.188756000000003</v>
+        <v>-2.683778327999998</v>
       </c>
       <c r="Q62">
-        <v>34.988756</v>
+        <v>23.116221672</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1805843608006352</v>
+        <v>0.1852883949840582</v>
       </c>
       <c r="T62">
-        <v>2.272657957223977</v>
+        <v>2.351974731473645</v>
       </c>
       <c r="U62">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V62">
-        <v>0.18</v>
+        <v>0.1638476768905387</v>
       </c>
       <c r="W62">
-        <v>0.0738</v>
+        <v>0.1227471610324689</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y62">
-        <v>1.509488865246292</v>
+        <v>0.910264871614104</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6411,22 +6411,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1471382422735887</v>
+        <v>0.1481482422735887</v>
       </c>
       <c r="C63">
-        <v>12.59531048751833</v>
+        <v>6.495878093711497</v>
       </c>
       <c r="D63">
-        <v>205.3483104875183</v>
+        <v>203.3218780937115</v>
       </c>
       <c r="E63">
-        <v>133.953</v>
+        <v>138.026</v>
       </c>
       <c r="F63">
-        <v>248.453</v>
+        <v>252.526</v>
       </c>
       <c r="G63">
         <v>55.7</v>
@@ -6447,37 +6447,37 @@
         <v>33.2</v>
       </c>
       <c r="M63">
-        <v>36.4729004</v>
+        <v>37.0708168</v>
       </c>
       <c r="N63">
-        <v>-3.272900399999997</v>
+        <v>-3.8708168</v>
       </c>
       <c r="O63">
-        <v>-0.5891220719999996</v>
+        <v>-0.696747024</v>
       </c>
       <c r="P63">
-        <v>-2.683778327999998</v>
+        <v>-3.174069776</v>
       </c>
       <c r="Q63">
-        <v>23.116221672</v>
+        <v>22.625930224</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1852883949840582</v>
+        <v>0.1889591422204808</v>
       </c>
       <c r="T63">
-        <v>2.351974731473645</v>
+        <v>2.413868803354531</v>
       </c>
       <c r="U63">
         <v>0.1468</v>
       </c>
       <c r="V63">
-        <v>0.1638476768905387</v>
+        <v>0.1612049724245623</v>
       </c>
       <c r="W63">
-        <v>0.1227471610324689</v>
+        <v>0.1231351100480743</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.910264871614104</v>
+        <v>0.8955831801364571</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6493,22 +6493,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1481482422735887</v>
+        <v>0.1491582422735888</v>
       </c>
       <c r="C64">
-        <v>6.495878093711497</v>
+        <v>0.4360496380660948</v>
       </c>
       <c r="D64">
-        <v>203.3218780937115</v>
+        <v>201.3350496380661</v>
       </c>
       <c r="E64">
-        <v>138.026</v>
+        <v>142.099</v>
       </c>
       <c r="F64">
-        <v>252.526</v>
+        <v>256.599</v>
       </c>
       <c r="G64">
         <v>55.7</v>
@@ -6529,37 +6529,37 @@
         <v>33.2</v>
       </c>
       <c r="M64">
-        <v>37.0708168</v>
+        <v>37.66873320000001</v>
       </c>
       <c r="N64">
-        <v>-3.8708168</v>
+        <v>-4.468733200000003</v>
       </c>
       <c r="O64">
-        <v>-0.696747024</v>
+        <v>-0.8043719760000004</v>
       </c>
       <c r="P64">
-        <v>-3.174069776</v>
+        <v>-3.664361224000002</v>
       </c>
       <c r="Q64">
-        <v>22.625930224</v>
+        <v>22.135638776</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1889591422204808</v>
+        <v>0.1928283082264398</v>
       </c>
       <c r="T64">
-        <v>2.413868803354531</v>
+        <v>2.479108500742491</v>
       </c>
       <c r="U64">
         <v>0.1468</v>
       </c>
       <c r="V64">
-        <v>0.1612049724245623</v>
+        <v>0.1586461633384581</v>
       </c>
       <c r="W64">
-        <v>0.1231351100480743</v>
+        <v>0.1235107432219144</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6567,7 +6567,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.8955831801364571</v>
+        <v>0.8813675741025451</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6575,22 +6575,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1491582422735888</v>
+        <v>0.1501682422735888</v>
       </c>
       <c r="C65">
-        <v>0.4360496380660948</v>
+        <v>-5.585324653812791</v>
       </c>
       <c r="D65">
-        <v>201.3350496380661</v>
+        <v>199.3866753461872</v>
       </c>
       <c r="E65">
-        <v>142.099</v>
+        <v>146.172</v>
       </c>
       <c r="F65">
-        <v>256.599</v>
+        <v>260.672</v>
       </c>
       <c r="G65">
         <v>55.7</v>
@@ -6611,37 +6611,37 @@
         <v>33.2</v>
       </c>
       <c r="M65">
-        <v>37.66873320000001</v>
+        <v>38.26664960000001</v>
       </c>
       <c r="N65">
-        <v>-4.468733200000003</v>
+        <v>-5.066649600000005</v>
       </c>
       <c r="O65">
-        <v>-0.8043719760000004</v>
+        <v>-0.9119969280000009</v>
       </c>
       <c r="P65">
-        <v>-3.664361224000002</v>
+        <v>-4.154652672000005</v>
       </c>
       <c r="Q65">
-        <v>22.135638776</v>
+        <v>21.645347328</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1928283082264398</v>
+        <v>0.1969124278993964</v>
       </c>
       <c r="T65">
-        <v>2.479108500742491</v>
+        <v>2.547972625763116</v>
       </c>
       <c r="U65">
         <v>0.1468</v>
       </c>
       <c r="V65">
-        <v>0.1586461633384581</v>
+        <v>0.1561673170362947</v>
       </c>
       <c r="W65">
-        <v>0.1235107432219144</v>
+        <v>0.1238746378590719</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6649,7 +6649,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.8813675741025451</v>
+        <v>0.8675962057571927</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1501682422735888</v>
+        <v>0.1511782422735888</v>
       </c>
       <c r="C66">
-        <v>-5.585324653812791</v>
+        <v>-11.56935047617191</v>
       </c>
       <c r="D66">
-        <v>199.3866753461872</v>
+        <v>197.4756495238281</v>
       </c>
       <c r="E66">
-        <v>146.172</v>
+        <v>150.245</v>
       </c>
       <c r="F66">
-        <v>260.672</v>
+        <v>264.745</v>
       </c>
       <c r="G66">
         <v>55.7</v>
@@ -6693,37 +6693,37 @@
         <v>33.2</v>
       </c>
       <c r="M66">
-        <v>38.26664960000001</v>
+        <v>38.864566</v>
       </c>
       <c r="N66">
-        <v>-5.066649600000005</v>
+        <v>-5.664566000000001</v>
       </c>
       <c r="O66">
-        <v>-0.9119969280000009</v>
+        <v>-1.01962188</v>
       </c>
       <c r="P66">
-        <v>-4.154652672000005</v>
+        <v>-4.644944120000001</v>
       </c>
       <c r="Q66">
-        <v>21.645347328</v>
+        <v>21.15505588</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1969124278993964</v>
+        <v>0.2012299258393792</v>
       </c>
       <c r="T66">
-        <v>2.547972625763116</v>
+        <v>2.620771843642062</v>
       </c>
       <c r="U66">
         <v>0.1468</v>
       </c>
       <c r="V66">
-        <v>0.1561673170362947</v>
+        <v>0.153764742928044</v>
       </c>
       <c r="W66">
-        <v>0.1238746378590719</v>
+        <v>0.1242273357381631</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6731,7 +6731,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.8675962057571927</v>
+        <v>0.8542485718224668</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6739,22 +6739,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1511782422735888</v>
+        <v>0.1521882422735888</v>
       </c>
       <c r="C67">
-        <v>-11.56935047617191</v>
+        <v>-17.51709153549092</v>
       </c>
       <c r="D67">
-        <v>197.4756495238281</v>
+        <v>195.6009084645091</v>
       </c>
       <c r="E67">
-        <v>150.245</v>
+        <v>154.318</v>
       </c>
       <c r="F67">
-        <v>264.745</v>
+        <v>268.818</v>
       </c>
       <c r="G67">
         <v>55.7</v>
@@ -6775,37 +6775,37 @@
         <v>33.2</v>
       </c>
       <c r="M67">
-        <v>38.864566</v>
+        <v>39.46248240000001</v>
       </c>
       <c r="N67">
-        <v>-5.664566000000001</v>
+        <v>-6.26248240000001</v>
       </c>
       <c r="O67">
-        <v>-1.01962188</v>
+        <v>-1.127246832000002</v>
       </c>
       <c r="P67">
-        <v>-4.644944120000001</v>
+        <v>-5.135235568000009</v>
       </c>
       <c r="Q67">
-        <v>21.15505588</v>
+        <v>20.66476443199999</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2012299258393792</v>
+        <v>0.2058013942464197</v>
       </c>
       <c r="T67">
-        <v>2.620771843642062</v>
+        <v>2.697853368455064</v>
       </c>
       <c r="U67">
         <v>0.1468</v>
       </c>
       <c r="V67">
-        <v>0.153764742928044</v>
+        <v>0.1514349740958009</v>
       </c>
       <c r="W67">
-        <v>0.1242273357381631</v>
+        <v>0.1245693458027364</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6813,7 +6813,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.8542485718224668</v>
+        <v>0.8413054116433383</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6821,22 +6821,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1521882422735888</v>
+        <v>0.1531982422735887</v>
       </c>
       <c r="C68">
-        <v>-17.51709153549092</v>
+        <v>-23.42957152479914</v>
       </c>
       <c r="D68">
-        <v>195.6009084645091</v>
+        <v>193.7614284752009</v>
       </c>
       <c r="E68">
-        <v>154.318</v>
+        <v>158.391</v>
       </c>
       <c r="F68">
-        <v>268.818</v>
+        <v>272.891</v>
       </c>
       <c r="G68">
         <v>55.7</v>
@@ -6857,37 +6857,37 @@
         <v>33.2</v>
       </c>
       <c r="M68">
-        <v>39.46248240000001</v>
+        <v>40.06039880000001</v>
       </c>
       <c r="N68">
-        <v>-6.26248240000001</v>
+        <v>-6.860398800000006</v>
       </c>
       <c r="O68">
-        <v>-1.127246832000002</v>
+        <v>-1.234871784000001</v>
       </c>
       <c r="P68">
-        <v>-5.135235568000009</v>
+        <v>-5.625527016000005</v>
       </c>
       <c r="Q68">
-        <v>20.66476443199999</v>
+        <v>20.174472984</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2058013942464197</v>
+        <v>0.2106499213447961</v>
       </c>
       <c r="T68">
-        <v>2.697853368455064</v>
+        <v>2.779606500832491</v>
       </c>
       <c r="U68">
         <v>0.1468</v>
       </c>
       <c r="V68">
-        <v>0.1514349740958009</v>
+        <v>0.1491747506018337</v>
       </c>
       <c r="W68">
-        <v>0.1245693458027364</v>
+        <v>0.1249011466116508</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.8413054116433383</v>
+        <v>0.8287486144546319</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6903,22 +6903,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1531982422735887</v>
+        <v>0.1542082422735888</v>
       </c>
       <c r="C69">
-        <v>-23.42957152479914</v>
+        <v>-29.30777598763029</v>
       </c>
       <c r="D69">
-        <v>193.7614284752009</v>
+        <v>191.9562240123697</v>
       </c>
       <c r="E69">
-        <v>158.391</v>
+        <v>162.4640000000001</v>
       </c>
       <c r="F69">
-        <v>272.891</v>
+        <v>276.9640000000001</v>
       </c>
       <c r="G69">
         <v>55.7</v>
@@ -6939,37 +6939,37 @@
         <v>33.2</v>
       </c>
       <c r="M69">
-        <v>40.06039880000001</v>
+        <v>40.65831520000001</v>
       </c>
       <c r="N69">
-        <v>-6.860398800000006</v>
+        <v>-7.458315200000008</v>
       </c>
       <c r="O69">
-        <v>-1.234871784000001</v>
+        <v>-1.342496736000002</v>
       </c>
       <c r="P69">
-        <v>-5.625527016000005</v>
+        <v>-6.115818464000007</v>
       </c>
       <c r="Q69">
-        <v>20.174472984</v>
+        <v>19.68418153599999</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2106499213447961</v>
+        <v>0.215801481386821</v>
       </c>
       <c r="T69">
-        <v>2.779606500832491</v>
+        <v>2.866469203983506</v>
       </c>
       <c r="U69">
         <v>0.1468</v>
       </c>
       <c r="V69">
-        <v>0.1491747506018337</v>
+        <v>0.1469810042694538</v>
       </c>
       <c r="W69">
-        <v>0.1249011466116508</v>
+        <v>0.1252231885732442</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.8287486144546319</v>
+        <v>0.816561134830299</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6985,22 +6985,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1542082422735888</v>
+        <v>0.1552182422735888</v>
       </c>
       <c r="C70">
-        <v>-29.30777598763029</v>
+        <v>-35.1526540787417</v>
       </c>
       <c r="D70">
-        <v>191.9562240123697</v>
+        <v>190.1843459212583</v>
       </c>
       <c r="E70">
-        <v>162.4640000000001</v>
+        <v>166.537</v>
       </c>
       <c r="F70">
-        <v>276.9640000000001</v>
+        <v>281.037</v>
       </c>
       <c r="G70">
         <v>55.7</v>
@@ -7021,37 +7021,37 @@
         <v>33.2</v>
       </c>
       <c r="M70">
-        <v>40.65831520000001</v>
+        <v>41.25623160000001</v>
       </c>
       <c r="N70">
-        <v>-7.458315200000008</v>
+        <v>-8.056231600000004</v>
       </c>
       <c r="O70">
-        <v>-1.342496736000002</v>
+        <v>-1.450121688000001</v>
       </c>
       <c r="P70">
-        <v>-6.115818464000007</v>
+        <v>-6.606109912000003</v>
       </c>
       <c r="Q70">
-        <v>19.68418153599999</v>
+        <v>19.193890088</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.215801481386821</v>
+        <v>0.2212854001412346</v>
       </c>
       <c r="T70">
-        <v>2.866469203983506</v>
+        <v>2.958935952499103</v>
       </c>
       <c r="U70">
         <v>0.1468</v>
       </c>
       <c r="V70">
-        <v>0.1469810042694538</v>
+        <v>0.1448508447872878</v>
       </c>
       <c r="W70">
-        <v>0.1252231885732442</v>
+        <v>0.1255358959852262</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7059,7 +7059,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.816561134830299</v>
+        <v>0.8047269154849324</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7067,22 +7067,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1552182422735888</v>
+        <v>0.1956527987536818</v>
       </c>
       <c r="C71">
-        <v>-35.1526540787417</v>
+        <v>-90.54281158757823</v>
       </c>
       <c r="D71">
-        <v>190.1843459212583</v>
+        <v>138.8671884124218</v>
       </c>
       <c r="E71">
-        <v>166.537</v>
+        <v>170.61</v>
       </c>
       <c r="F71">
-        <v>281.037</v>
+        <v>285.11</v>
       </c>
       <c r="G71">
         <v>55.7</v>
@@ -7103,45 +7103,45 @@
         <v>33.2</v>
       </c>
       <c r="M71">
-        <v>41.25623160000001</v>
+        <v>57.25008800000001</v>
       </c>
       <c r="N71">
-        <v>-8.056231600000004</v>
+        <v>-24.050088</v>
       </c>
       <c r="O71">
-        <v>-1.450121688000001</v>
+        <v>-4.32901584</v>
       </c>
       <c r="P71">
-        <v>-6.606109912000003</v>
+        <v>-19.72107216</v>
       </c>
       <c r="Q71">
-        <v>19.193890088</v>
+        <v>6.078927839999999</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2212854001412346</v>
+        <v>0.2325501017462526</v>
       </c>
       <c r="T71">
-        <v>2.958935952499103</v>
+        <v>3.14887500467345</v>
       </c>
       <c r="U71">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V71">
-        <v>0.1448508447872878</v>
+        <v>0.1043841190252843</v>
       </c>
       <c r="W71">
-        <v>0.1255358959852262</v>
+        <v>0.1798396688997229</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y71">
-        <v>0.8047269154849324</v>
+        <v>0.5799117723626905</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7149,22 +7149,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1956527987536818</v>
+        <v>0.1972027987536818</v>
       </c>
       <c r="C72">
-        <v>-90.54281158757823</v>
+        <v>-96.03747713016469</v>
       </c>
       <c r="D72">
-        <v>138.8671884124218</v>
+        <v>137.4455228698354</v>
       </c>
       <c r="E72">
-        <v>170.61</v>
+        <v>174.683</v>
       </c>
       <c r="F72">
-        <v>285.11</v>
+        <v>289.183</v>
       </c>
       <c r="G72">
         <v>55.7</v>
@@ -7185,37 +7185,37 @@
         <v>33.2</v>
       </c>
       <c r="M72">
-        <v>57.25008800000001</v>
+        <v>58.06794640000001</v>
       </c>
       <c r="N72">
-        <v>-24.050088</v>
+        <v>-24.86794640000001</v>
       </c>
       <c r="O72">
-        <v>-4.32901584</v>
+        <v>-4.476230352000001</v>
       </c>
       <c r="P72">
-        <v>-19.72107216</v>
+        <v>-20.39171604800001</v>
       </c>
       <c r="Q72">
-        <v>6.078927839999999</v>
+        <v>5.408283951999994</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2325501017462526</v>
+        <v>0.2389897604271579</v>
       </c>
       <c r="T72">
-        <v>3.14887500467345</v>
+        <v>3.257456901386328</v>
       </c>
       <c r="U72">
         <v>0.2008</v>
       </c>
       <c r="V72">
-        <v>0.1043841190252843</v>
+        <v>0.1029139201657732</v>
       </c>
       <c r="W72">
-        <v>0.1798396688997229</v>
+        <v>0.1801348848307127</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7223,7 +7223,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.5799117723626905</v>
+        <v>0.5717440009209624</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7231,22 +7231,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1972027987536818</v>
+        <v>0.1987527987536818</v>
       </c>
       <c r="C73">
-        <v>-96.03747713016458</v>
+        <v>-101.5033287954115</v>
       </c>
       <c r="D73">
-        <v>137.4455228698354</v>
+        <v>136.0526712045885</v>
       </c>
       <c r="E73">
-        <v>174.683</v>
+        <v>178.756</v>
       </c>
       <c r="F73">
-        <v>289.183</v>
+        <v>293.256</v>
       </c>
       <c r="G73">
         <v>55.7</v>
@@ -7267,37 +7267,37 @@
         <v>33.2</v>
       </c>
       <c r="M73">
-        <v>58.0679464</v>
+        <v>58.8858048</v>
       </c>
       <c r="N73">
-        <v>-24.8679464</v>
+        <v>-25.68580479999999</v>
       </c>
       <c r="O73">
-        <v>-4.476230352</v>
+        <v>-4.623444863999999</v>
       </c>
       <c r="P73">
-        <v>-20.391716048</v>
+        <v>-21.06235993599999</v>
       </c>
       <c r="Q73">
-        <v>5.408283952000001</v>
+        <v>4.737640064000008</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2389897604271578</v>
+        <v>0.2458893947281277</v>
       </c>
       <c r="T73">
-        <v>3.257456901386327</v>
+        <v>3.37379464786441</v>
       </c>
       <c r="U73">
         <v>0.2008</v>
       </c>
       <c r="V73">
-        <v>0.1029139201657732</v>
+        <v>0.1014845601634709</v>
       </c>
       <c r="W73">
-        <v>0.1801348848307127</v>
+        <v>0.1804219003191751</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7305,7 +7305,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.5717440009209624</v>
+        <v>0.5638031120192826</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7313,22 +7313,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1987527987536818</v>
+        <v>0.2003027987536818</v>
       </c>
       <c r="C74">
-        <v>-101.5033287954115</v>
+        <v>-106.9412337813937</v>
       </c>
       <c r="D74">
-        <v>136.0526712045885</v>
+        <v>134.6877662186062</v>
       </c>
       <c r="E74">
-        <v>178.756</v>
+        <v>182.829</v>
       </c>
       <c r="F74">
-        <v>293.256</v>
+        <v>297.329</v>
       </c>
       <c r="G74">
         <v>55.7</v>
@@ -7349,37 +7349,37 @@
         <v>33.2</v>
       </c>
       <c r="M74">
-        <v>58.8858048</v>
+        <v>59.7036632</v>
       </c>
       <c r="N74">
-        <v>-25.68580479999999</v>
+        <v>-26.5036632</v>
       </c>
       <c r="O74">
-        <v>-4.623444863999999</v>
+        <v>-4.770659375999999</v>
       </c>
       <c r="P74">
-        <v>-21.06235993599999</v>
+        <v>-21.733003824</v>
       </c>
       <c r="Q74">
-        <v>4.737640064000008</v>
+        <v>4.066996176</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2458893947281277</v>
+        <v>0.2533001130513917</v>
       </c>
       <c r="T74">
-        <v>3.37379464786441</v>
+        <v>3.498750005192721</v>
       </c>
       <c r="U74">
         <v>0.2008</v>
       </c>
       <c r="V74">
-        <v>0.1014845601634709</v>
+        <v>0.1000943607091767</v>
       </c>
       <c r="W74">
-        <v>0.1804219003191751</v>
+        <v>0.1807010523695973</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7387,7 +7387,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.5638031120192826</v>
+        <v>0.5560797817176485</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7395,22 +7395,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2003027987536818</v>
+        <v>0.2018527987536818</v>
       </c>
       <c r="C75">
-        <v>-106.9412337813937</v>
+        <v>-112.3520248322827</v>
       </c>
       <c r="D75">
-        <v>134.6877662186062</v>
+        <v>133.3499751677173</v>
       </c>
       <c r="E75">
-        <v>182.829</v>
+        <v>186.902</v>
       </c>
       <c r="F75">
-        <v>297.329</v>
+        <v>301.402</v>
       </c>
       <c r="G75">
         <v>55.7</v>
@@ -7431,37 +7431,37 @@
         <v>33.2</v>
       </c>
       <c r="M75">
-        <v>59.7036632</v>
+        <v>60.5215216</v>
       </c>
       <c r="N75">
-        <v>-26.5036632</v>
+        <v>-27.3215216</v>
       </c>
       <c r="O75">
-        <v>-4.770659375999999</v>
+        <v>-4.917873887999999</v>
       </c>
       <c r="P75">
-        <v>-21.733003824</v>
+        <v>-22.403647712</v>
       </c>
       <c r="Q75">
-        <v>4.066996176</v>
+        <v>3.396352288000003</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2533001130513917</v>
+        <v>0.2612808866302914</v>
       </c>
       <c r="T75">
-        <v>3.498750005192721</v>
+        <v>3.633317313084749</v>
       </c>
       <c r="U75">
         <v>0.2008</v>
       </c>
       <c r="V75">
-        <v>0.1000943607091767</v>
+        <v>0.09874173421310678</v>
       </c>
       <c r="W75">
-        <v>0.1807010523695973</v>
+        <v>0.1809726597700082</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7469,7 +7469,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.5560797817176485</v>
+        <v>0.5485651900728155</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7477,22 +7477,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2018527987536818</v>
+        <v>0.2034027987536818</v>
       </c>
       <c r="C76">
-        <v>-112.3520248322827</v>
+        <v>-117.7365019325911</v>
       </c>
       <c r="D76">
-        <v>133.3499751677173</v>
+        <v>132.0384980674089</v>
       </c>
       <c r="E76">
-        <v>186.902</v>
+        <v>190.975</v>
       </c>
       <c r="F76">
-        <v>301.402</v>
+        <v>305.475</v>
       </c>
       <c r="G76">
         <v>55.7</v>
@@ -7513,37 +7513,37 @@
         <v>33.2</v>
       </c>
       <c r="M76">
-        <v>60.5215216</v>
+        <v>61.33938000000001</v>
       </c>
       <c r="N76">
-        <v>-27.3215216</v>
+        <v>-28.13938</v>
       </c>
       <c r="O76">
-        <v>-4.917873887999999</v>
+        <v>-5.0650884</v>
       </c>
       <c r="P76">
-        <v>-22.403647712</v>
+        <v>-23.0742916</v>
       </c>
       <c r="Q76">
-        <v>3.396352288000003</v>
+        <v>2.725708399999998</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2612808866302914</v>
+        <v>0.2699001220955031</v>
       </c>
       <c r="T76">
-        <v>3.633317313084749</v>
+        <v>3.77865000560814</v>
       </c>
       <c r="U76">
         <v>0.2008</v>
       </c>
       <c r="V76">
-        <v>0.09874173421310678</v>
+        <v>0.09742517775693202</v>
       </c>
       <c r="W76">
-        <v>0.1809726597700082</v>
+        <v>0.1812370243064081</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.5485651900728155</v>
+        <v>0.5412509875385112</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7559,22 +7559,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2034027987536818</v>
+        <v>0.2049527987536818</v>
       </c>
       <c r="C77">
-        <v>-117.7365019325911</v>
+        <v>-123.0954339024161</v>
       </c>
       <c r="D77">
-        <v>132.0384980674089</v>
+        <v>130.7525660975839</v>
       </c>
       <c r="E77">
-        <v>190.975</v>
+        <v>195.048</v>
       </c>
       <c r="F77">
-        <v>305.475</v>
+        <v>309.548</v>
       </c>
       <c r="G77">
         <v>55.7</v>
@@ -7595,37 +7595,37 @@
         <v>33.2</v>
       </c>
       <c r="M77">
-        <v>61.33938000000001</v>
+        <v>62.1572384</v>
       </c>
       <c r="N77">
-        <v>-28.13938</v>
+        <v>-28.9572384</v>
       </c>
       <c r="O77">
-        <v>-5.0650884</v>
+        <v>-5.212302912</v>
       </c>
       <c r="P77">
-        <v>-23.0742916</v>
+        <v>-23.744935488</v>
       </c>
       <c r="Q77">
-        <v>2.725708399999998</v>
+        <v>2.055064511999998</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2699001220955031</v>
+        <v>0.2792376271828157</v>
       </c>
       <c r="T77">
-        <v>3.77865000560814</v>
+        <v>3.936093755841812</v>
       </c>
       <c r="U77">
         <v>0.2008</v>
       </c>
       <c r="V77">
-        <v>0.09742517775693202</v>
+        <v>0.09614326752328815</v>
       </c>
       <c r="W77">
-        <v>0.1812370243064081</v>
+        <v>0.1814944318813237</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7633,7 +7633,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.5412509875385112</v>
+        <v>0.5341292640182675</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7641,22 +7641,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2049527987536818</v>
+        <v>0.2065027987536818</v>
       </c>
       <c r="C78">
-        <v>-123.0954339024161</v>
+        <v>-128.429559900364</v>
       </c>
       <c r="D78">
-        <v>130.7525660975839</v>
+        <v>129.491440099636</v>
       </c>
       <c r="E78">
-        <v>195.048</v>
+        <v>199.121</v>
       </c>
       <c r="F78">
-        <v>309.548</v>
+        <v>313.621</v>
       </c>
       <c r="G78">
         <v>55.7</v>
@@ -7677,37 +7677,37 @@
         <v>33.2</v>
       </c>
       <c r="M78">
-        <v>62.1572384</v>
+        <v>62.97509680000001</v>
       </c>
       <c r="N78">
-        <v>-28.9572384</v>
+        <v>-29.77509680000001</v>
       </c>
       <c r="O78">
-        <v>-5.212302912</v>
+        <v>-5.359517424000001</v>
       </c>
       <c r="P78">
-        <v>-23.744935488</v>
+        <v>-24.41557937600001</v>
       </c>
       <c r="Q78">
-        <v>2.055064511999998</v>
+        <v>1.384420623999993</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2792376271828157</v>
+        <v>0.2893870892342424</v>
       </c>
       <c r="T78">
-        <v>3.936093755841812</v>
+        <v>4.107228266965369</v>
       </c>
       <c r="U78">
         <v>0.2008</v>
       </c>
       <c r="V78">
-        <v>0.09614326752328815</v>
+        <v>0.09489465365934935</v>
       </c>
       <c r="W78">
-        <v>0.1814944318813237</v>
+        <v>0.1817451535452027</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7715,7 +7715,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.5341292640182675</v>
+        <v>0.5271925203297186</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7723,22 +7723,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2065027987536818</v>
+        <v>0.2080527987536818</v>
       </c>
       <c r="C79">
-        <v>-128.429559900364</v>
+        <v>-133.7395908403303</v>
       </c>
       <c r="D79">
-        <v>129.491440099636</v>
+        <v>128.2544091596697</v>
       </c>
       <c r="E79">
-        <v>199.121</v>
+        <v>203.194</v>
       </c>
       <c r="F79">
-        <v>313.621</v>
+        <v>317.694</v>
       </c>
       <c r="G79">
         <v>55.7</v>
@@ -7759,37 +7759,37 @@
         <v>33.2</v>
       </c>
       <c r="M79">
-        <v>62.97509680000001</v>
+        <v>63.79295520000001</v>
       </c>
       <c r="N79">
-        <v>-29.77509680000001</v>
+        <v>-30.59295520000001</v>
       </c>
       <c r="O79">
-        <v>-5.359517424000001</v>
+        <v>-5.506731936</v>
       </c>
       <c r="P79">
-        <v>-24.41557937600001</v>
+        <v>-25.086223264</v>
       </c>
       <c r="Q79">
-        <v>1.384420623999993</v>
+        <v>0.7137767359999962</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2893870892342424</v>
+        <v>0.3004592296539808</v>
       </c>
       <c r="T79">
-        <v>4.107228266965369</v>
+        <v>4.293920460918341</v>
       </c>
       <c r="U79">
         <v>0.2008</v>
       </c>
       <c r="V79">
-        <v>0.09489465365934935</v>
+        <v>0.09367805553551153</v>
       </c>
       <c r="W79">
-        <v>0.1817451535452027</v>
+        <v>0.1819894464484693</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7797,7 +7797,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.5271925203297186</v>
+        <v>0.520433641863953</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7805,22 +7805,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2080527987536818</v>
+        <v>0.2096027987536818</v>
       </c>
       <c r="C80">
-        <v>-133.7395908403303</v>
+        <v>-139.0262107278416</v>
       </c>
       <c r="D80">
-        <v>128.2544091596697</v>
+        <v>127.0407892721584</v>
       </c>
       <c r="E80">
-        <v>203.194</v>
+        <v>207.267</v>
       </c>
       <c r="F80">
-        <v>317.694</v>
+        <v>321.767</v>
       </c>
       <c r="G80">
         <v>55.7</v>
@@ -7841,37 +7841,37 @@
         <v>33.2</v>
       </c>
       <c r="M80">
-        <v>63.79295520000001</v>
+        <v>64.6108136</v>
       </c>
       <c r="N80">
-        <v>-30.59295520000001</v>
+        <v>-31.4108136</v>
       </c>
       <c r="O80">
-        <v>-5.506731936</v>
+        <v>-5.653946447999999</v>
       </c>
       <c r="P80">
-        <v>-25.086223264</v>
+        <v>-25.756867152</v>
       </c>
       <c r="Q80">
-        <v>0.7137767359999962</v>
+        <v>0.04313284800000261</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.3004592296539808</v>
+        <v>0.3125858596375037</v>
       </c>
       <c r="T80">
-        <v>4.293920460918341</v>
+        <v>4.498392863819214</v>
       </c>
       <c r="U80">
         <v>0.2008</v>
       </c>
       <c r="V80">
-        <v>0.09367805553551153</v>
+        <v>0.09249225736417596</v>
       </c>
       <c r="W80">
-        <v>0.1819894464484693</v>
+        <v>0.1822275547212735</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7879,7 +7879,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.520433641863953</v>
+        <v>0.5138458742454219</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7887,22 +7887,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2096027987536818</v>
+        <v>0.2111527987536818</v>
       </c>
       <c r="C81">
-        <v>-139.0262107278416</v>
+        <v>-144.2900779212369</v>
       </c>
       <c r="D81">
-        <v>127.0407892721584</v>
+        <v>125.8499220787631</v>
       </c>
       <c r="E81">
-        <v>207.267</v>
+        <v>211.34</v>
       </c>
       <c r="F81">
-        <v>321.767</v>
+        <v>325.84</v>
       </c>
       <c r="G81">
         <v>55.7</v>
@@ -7923,37 +7923,37 @@
         <v>33.2</v>
       </c>
       <c r="M81">
-        <v>64.6108136</v>
+        <v>65.42867200000001</v>
       </c>
       <c r="N81">
-        <v>-31.4108136</v>
+        <v>-32.228672</v>
       </c>
       <c r="O81">
-        <v>-5.653946447999999</v>
+        <v>-5.801160960000001</v>
       </c>
       <c r="P81">
-        <v>-25.756867152</v>
+        <v>-26.42751104</v>
       </c>
       <c r="Q81">
-        <v>0.04313284800000261</v>
+        <v>-0.6275110400000017</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.3125858596375037</v>
+        <v>0.3259251526193789</v>
       </c>
       <c r="T81">
-        <v>4.498392863819214</v>
+        <v>4.723312507010175</v>
       </c>
       <c r="U81">
         <v>0.2008</v>
       </c>
       <c r="V81">
-        <v>0.09249225736417596</v>
+        <v>0.09133610414712376</v>
       </c>
       <c r="W81">
-        <v>0.1822275547212735</v>
+        <v>0.1824597102872575</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7961,7 +7961,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.5138458742454219</v>
+        <v>0.5074228008173542</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7969,22 +7969,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2111527987536818</v>
+        <v>0.2127027987536818</v>
       </c>
       <c r="C82">
-        <v>-144.2900779212369</v>
+        <v>-149.5318263225741</v>
       </c>
       <c r="D82">
-        <v>125.8499220787631</v>
+        <v>124.6811736774258</v>
       </c>
       <c r="E82">
-        <v>211.34</v>
+        <v>215.413</v>
       </c>
       <c r="F82">
-        <v>325.84</v>
+        <v>329.913</v>
       </c>
       <c r="G82">
         <v>55.7</v>
@@ -8005,37 +8005,37 @@
         <v>33.2</v>
       </c>
       <c r="M82">
-        <v>65.42867200000001</v>
+        <v>66.2465304</v>
       </c>
       <c r="N82">
-        <v>-32.228672</v>
+        <v>-33.04653039999999</v>
       </c>
       <c r="O82">
-        <v>-5.801160960000001</v>
+        <v>-5.948375471999999</v>
       </c>
       <c r="P82">
-        <v>-26.42751104</v>
+        <v>-27.098154928</v>
       </c>
       <c r="Q82">
-        <v>-0.6275110400000017</v>
+        <v>-1.298154927999995</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3259251526193789</v>
+        <v>0.3406685817046093</v>
       </c>
       <c r="T82">
-        <v>4.723312507010175</v>
+        <v>4.971907902115974</v>
       </c>
       <c r="U82">
         <v>0.2008</v>
       </c>
       <c r="V82">
-        <v>0.09133610414712376</v>
+        <v>0.0902084979230852</v>
       </c>
       <c r="W82">
-        <v>0.1824597102872575</v>
+        <v>0.1826861336170445</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8043,7 +8043,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.5074228008173542</v>
+        <v>0.5011583217949178</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8051,22 +8051,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2127027987536818</v>
+        <v>0.2436083269158656</v>
       </c>
       <c r="C83">
-        <v>-149.5318263225741</v>
+        <v>-173.0849846377536</v>
       </c>
       <c r="D83">
-        <v>124.6811736774258</v>
+        <v>105.2010153622465</v>
       </c>
       <c r="E83">
-        <v>215.413</v>
+        <v>219.486</v>
       </c>
       <c r="F83">
-        <v>329.913</v>
+        <v>333.986</v>
       </c>
       <c r="G83">
         <v>55.7</v>
@@ -8087,45 +8087,45 @@
         <v>33.2</v>
       </c>
       <c r="M83">
-        <v>66.2465304</v>
+        <v>78.75389880000002</v>
       </c>
       <c r="N83">
-        <v>-33.04653039999999</v>
+        <v>-45.55389880000001</v>
       </c>
       <c r="O83">
-        <v>-5.948375471999999</v>
+        <v>-8.199701784000002</v>
       </c>
       <c r="P83">
-        <v>-27.098154928</v>
+        <v>-37.35419701600001</v>
       </c>
       <c r="Q83">
-        <v>-1.298154927999995</v>
+        <v>-11.55419701600001</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3406685817046093</v>
+        <v>0.3606919927003308</v>
       </c>
       <c r="T83">
-        <v>4.971907902115974</v>
+        <v>5.309531377568756</v>
       </c>
       <c r="U83">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.0902084979230852</v>
+        <v>0.0758819574784023</v>
       </c>
       <c r="W83">
-        <v>0.1826861336170445</v>
+        <v>0.2179070344265927</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y83">
-        <v>0.5011583217949178</v>
+        <v>0.4215664304355684</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8133,22 +8133,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2436083269158656</v>
+        <v>0.2455083269158655</v>
       </c>
       <c r="C84">
-        <v>-173.0849846377536</v>
+        <v>-178.158853916842</v>
       </c>
       <c r="D84">
-        <v>105.2010153622465</v>
+        <v>104.200146083158</v>
       </c>
       <c r="E84">
-        <v>219.486</v>
+        <v>223.559</v>
       </c>
       <c r="F84">
-        <v>333.986</v>
+        <v>338.059</v>
       </c>
       <c r="G84">
         <v>55.7</v>
@@ -8169,37 +8169,37 @@
         <v>33.2</v>
       </c>
       <c r="M84">
-        <v>78.75389880000002</v>
+        <v>79.71431220000001</v>
       </c>
       <c r="N84">
-        <v>-45.55389880000001</v>
+        <v>-46.51431220000001</v>
       </c>
       <c r="O84">
-        <v>-8.199701784000002</v>
+        <v>-8.372576196000001</v>
       </c>
       <c r="P84">
-        <v>-37.35419701600001</v>
+        <v>-38.14173600400001</v>
       </c>
       <c r="Q84">
-        <v>-11.55419701600001</v>
+        <v>-12.34173600400001</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3606919927003308</v>
+        <v>0.3792150510944678</v>
       </c>
       <c r="T84">
-        <v>5.309531377568756</v>
+        <v>5.62185675271986</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.0758819574784023</v>
+        <v>0.0749677170268553</v>
       </c>
       <c r="W84">
-        <v>0.2179070344265927</v>
+        <v>0.2181226123250675</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8207,7 +8207,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.4215664304355684</v>
+        <v>0.4164873168158628</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8215,22 +8215,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2455083269158655</v>
+        <v>0.2474083269158656</v>
       </c>
       <c r="C85">
-        <v>-178.158853916842</v>
+        <v>-183.2138583835555</v>
       </c>
       <c r="D85">
-        <v>104.200146083158</v>
+        <v>103.2181416164446</v>
       </c>
       <c r="E85">
-        <v>223.559</v>
+        <v>227.6320000000001</v>
       </c>
       <c r="F85">
-        <v>338.059</v>
+        <v>342.1320000000001</v>
       </c>
       <c r="G85">
         <v>55.7</v>
@@ -8251,37 +8251,37 @@
         <v>33.2</v>
       </c>
       <c r="M85">
-        <v>79.71431220000001</v>
+        <v>80.67472560000002</v>
       </c>
       <c r="N85">
-        <v>-46.51431220000001</v>
+        <v>-47.47472560000001</v>
       </c>
       <c r="O85">
-        <v>-8.372576196000001</v>
+        <v>-8.545450608000003</v>
       </c>
       <c r="P85">
-        <v>-38.14173600400001</v>
+        <v>-38.92927499200001</v>
       </c>
       <c r="Q85">
-        <v>-12.34173600400001</v>
+        <v>-13.12927499200001</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3792150510944678</v>
+        <v>0.4000534917878721</v>
       </c>
       <c r="T85">
-        <v>5.62185675271986</v>
+        <v>5.973222799764852</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.0749677170268553</v>
+        <v>0.07407524420510703</v>
       </c>
       <c r="W85">
-        <v>0.2181226123250675</v>
+        <v>0.2183330574164358</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.4164873168158628</v>
+        <v>0.4115291344728168</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8297,22 +8297,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2474083269158656</v>
+        <v>0.2493083269158655</v>
       </c>
       <c r="C86">
-        <v>-183.2138583835554</v>
+        <v>-188.2505264164233</v>
       </c>
       <c r="D86">
-        <v>103.2181416164446</v>
+        <v>102.2544735835767</v>
       </c>
       <c r="E86">
-        <v>227.632</v>
+        <v>231.705</v>
       </c>
       <c r="F86">
-        <v>342.132</v>
+        <v>346.205</v>
       </c>
       <c r="G86">
         <v>55.7</v>
@@ -8333,37 +8333,37 @@
         <v>33.2</v>
       </c>
       <c r="M86">
-        <v>80.6747256</v>
+        <v>81.635139</v>
       </c>
       <c r="N86">
-        <v>-47.4747256</v>
+        <v>-48.43513899999999</v>
       </c>
       <c r="O86">
-        <v>-8.545450607999999</v>
+        <v>-8.718325019999998</v>
       </c>
       <c r="P86">
-        <v>-38.929274992</v>
+        <v>-39.71681398</v>
       </c>
       <c r="Q86">
-        <v>-13.129274992</v>
+        <v>-13.91681398</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.4000534917878719</v>
+        <v>0.4236703912403967</v>
       </c>
       <c r="T86">
-        <v>5.973222799764848</v>
+        <v>6.371437653082505</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.07407524420510703</v>
+        <v>0.07320377074387048</v>
       </c>
       <c r="W86">
-        <v>0.2183330574164358</v>
+        <v>0.2185385508585953</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8371,7 +8371,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.4115291344728169</v>
+        <v>0.406687615243725</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8379,22 +8379,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2493083269158655</v>
+        <v>0.2512083269158656</v>
       </c>
       <c r="C87">
-        <v>-188.2505264164233</v>
+        <v>-193.2693668442478</v>
       </c>
       <c r="D87">
-        <v>102.2544735835767</v>
+        <v>101.3086331557523</v>
       </c>
       <c r="E87">
-        <v>231.705</v>
+        <v>235.778</v>
       </c>
       <c r="F87">
-        <v>346.205</v>
+        <v>350.278</v>
       </c>
       <c r="G87">
         <v>55.7</v>
@@ -8415,37 +8415,37 @@
         <v>33.2</v>
       </c>
       <c r="M87">
-        <v>81.635139</v>
+        <v>82.5955524</v>
       </c>
       <c r="N87">
-        <v>-48.43513899999999</v>
+        <v>-49.3955524</v>
       </c>
       <c r="O87">
-        <v>-8.718325019999998</v>
+        <v>-8.891199431999999</v>
       </c>
       <c r="P87">
-        <v>-39.71681398</v>
+        <v>-40.504352968</v>
       </c>
       <c r="Q87">
-        <v>-13.91681398</v>
+        <v>-14.704352968</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.4236703912403967</v>
+        <v>0.4506611334718536</v>
       </c>
       <c r="T87">
-        <v>6.371437653082505</v>
+        <v>6.826540342588398</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.07320377074387048</v>
+        <v>0.07235256410731385</v>
       </c>
       <c r="W87">
-        <v>0.2185385508585953</v>
+        <v>0.2187392653834954</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.406687615243725</v>
+        <v>0.401958689485077</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8461,22 +8461,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2512083269158656</v>
+        <v>0.2531083269158656</v>
       </c>
       <c r="C88">
-        <v>-193.2693668442478</v>
+        <v>-198.2708698419785</v>
       </c>
       <c r="D88">
-        <v>101.3086331557523</v>
+        <v>100.3801301580215</v>
       </c>
       <c r="E88">
-        <v>235.778</v>
+        <v>239.851</v>
       </c>
       <c r="F88">
-        <v>350.278</v>
+        <v>354.351</v>
       </c>
       <c r="G88">
         <v>55.7</v>
@@ -8497,37 +8497,37 @@
         <v>33.2</v>
       </c>
       <c r="M88">
-        <v>82.5955524</v>
+        <v>83.55596580000001</v>
       </c>
       <c r="N88">
-        <v>-49.3955524</v>
+        <v>-50.35596580000001</v>
       </c>
       <c r="O88">
-        <v>-8.891199431999999</v>
+        <v>-9.064073844000001</v>
       </c>
       <c r="P88">
-        <v>-40.504352968</v>
+        <v>-41.29189195600001</v>
       </c>
       <c r="Q88">
-        <v>-14.704352968</v>
+        <v>-15.49189195600001</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.4506611334718536</v>
+        <v>0.4818042975850732</v>
       </c>
       <c r="T88">
-        <v>6.826540342588398</v>
+        <v>7.351658830479814</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.07235256410731385</v>
+        <v>0.07152092543941369</v>
       </c>
       <c r="W88">
-        <v>0.2187392653834954</v>
+        <v>0.2189353657813863</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8535,7 +8535,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.401958689485077</v>
+        <v>0.3973384746634093</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8543,22 +8543,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2531083269158656</v>
+        <v>0.2550083269158656</v>
       </c>
       <c r="C89">
-        <v>-198.2708698419785</v>
+        <v>-203.2555077777713</v>
       </c>
       <c r="D89">
-        <v>100.3801301580215</v>
+        <v>99.46849222222875</v>
       </c>
       <c r="E89">
-        <v>239.851</v>
+        <v>243.924</v>
       </c>
       <c r="F89">
-        <v>354.351</v>
+        <v>358.424</v>
       </c>
       <c r="G89">
         <v>55.7</v>
@@ -8579,37 +8579,37 @@
         <v>33.2</v>
       </c>
       <c r="M89">
-        <v>83.55596580000001</v>
+        <v>84.51637920000002</v>
       </c>
       <c r="N89">
-        <v>-50.35596580000001</v>
+        <v>-51.31637920000001</v>
       </c>
       <c r="O89">
-        <v>-9.064073844000001</v>
+        <v>-9.236948256000002</v>
       </c>
       <c r="P89">
-        <v>-41.29189195600001</v>
+        <v>-42.07943094400001</v>
       </c>
       <c r="Q89">
-        <v>-15.49189195600001</v>
+        <v>-16.27943094400001</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4818042975850732</v>
+        <v>0.518137989050496</v>
       </c>
       <c r="T89">
-        <v>7.351658830479814</v>
+        <v>7.964297066353133</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.07152092543941369</v>
+        <v>0.07070818765032942</v>
       </c>
       <c r="W89">
-        <v>0.2189353657813863</v>
+        <v>0.2191270093520523</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8617,7 +8617,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3973384746634093</v>
+        <v>0.3928232647240524</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8625,22 +8625,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2550083269158656</v>
+        <v>0.2569083269158656</v>
       </c>
       <c r="C90">
-        <v>-203.2555077777713</v>
+        <v>-208.2237360143039</v>
       </c>
       <c r="D90">
-        <v>99.46849222222875</v>
+        <v>98.57326398569614</v>
       </c>
       <c r="E90">
-        <v>243.924</v>
+        <v>247.997</v>
       </c>
       <c r="F90">
-        <v>358.424</v>
+        <v>362.497</v>
       </c>
       <c r="G90">
         <v>55.7</v>
@@ -8661,37 +8661,37 @@
         <v>33.2</v>
       </c>
       <c r="M90">
-        <v>84.51637920000002</v>
+        <v>85.47679260000001</v>
       </c>
       <c r="N90">
-        <v>-51.31637920000001</v>
+        <v>-52.27679260000001</v>
       </c>
       <c r="O90">
-        <v>-9.236948256000002</v>
+        <v>-9.409822668</v>
       </c>
       <c r="P90">
-        <v>-42.07943094400001</v>
+        <v>-42.866969932</v>
       </c>
       <c r="Q90">
-        <v>-16.27943094400001</v>
+        <v>-17.066969932</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.518137989050496</v>
+        <v>0.5610778062369046</v>
       </c>
       <c r="T90">
-        <v>7.964297066353133</v>
+        <v>8.688324072385235</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.07070818765032942</v>
+        <v>0.06991371363178642</v>
       </c>
       <c r="W90">
-        <v>0.2191270093520523</v>
+        <v>0.2193143463256248</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3928232647240524</v>
+        <v>0.3884095201765911</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8707,22 +8707,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2569083269158656</v>
+        <v>0.2588083269158655</v>
       </c>
       <c r="C91">
-        <v>-208.2237360143039</v>
+        <v>-213.1759936672067</v>
       </c>
       <c r="D91">
-        <v>98.57326398569614</v>
+        <v>97.69400633279324</v>
       </c>
       <c r="E91">
-        <v>247.997</v>
+        <v>252.07</v>
       </c>
       <c r="F91">
-        <v>362.497</v>
+        <v>366.57</v>
       </c>
       <c r="G91">
         <v>55.7</v>
@@ -8743,37 +8743,37 @@
         <v>33.2</v>
       </c>
       <c r="M91">
-        <v>85.47679260000001</v>
+        <v>86.437206</v>
       </c>
       <c r="N91">
-        <v>-52.27679260000001</v>
+        <v>-53.237206</v>
       </c>
       <c r="O91">
-        <v>-9.409822668</v>
+        <v>-9.582697079999999</v>
       </c>
       <c r="P91">
-        <v>-42.866969932</v>
+        <v>-43.65450892</v>
       </c>
       <c r="Q91">
-        <v>-17.066969932</v>
+        <v>-17.85450892</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.5610778062369046</v>
+        <v>0.6126055868605952</v>
       </c>
       <c r="T91">
-        <v>8.688324072385235</v>
+        <v>9.55715647962376</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.06991371363178642</v>
+        <v>0.06913689459143324</v>
       </c>
       <c r="W91">
-        <v>0.2193143463256248</v>
+        <v>0.2194975202553401</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8781,7 +8781,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3884095201765911</v>
+        <v>0.3840938588412958</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8789,22 +8789,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2588083269158655</v>
+        <v>0.2607083269158655</v>
       </c>
       <c r="C92">
-        <v>-213.1759936672067</v>
+        <v>-218.1127043232623</v>
       </c>
       <c r="D92">
-        <v>97.69400633279324</v>
+        <v>96.83029567673768</v>
       </c>
       <c r="E92">
-        <v>252.07</v>
+        <v>256.143</v>
       </c>
       <c r="F92">
-        <v>366.57</v>
+        <v>370.643</v>
       </c>
       <c r="G92">
         <v>55.7</v>
@@ -8825,37 +8825,37 @@
         <v>33.2</v>
       </c>
       <c r="M92">
-        <v>86.437206</v>
+        <v>87.39761940000001</v>
       </c>
       <c r="N92">
-        <v>-53.237206</v>
+        <v>-54.19761940000001</v>
       </c>
       <c r="O92">
-        <v>-9.582697079999999</v>
+        <v>-9.755571492000001</v>
       </c>
       <c r="P92">
-        <v>-43.65450892</v>
+        <v>-44.44204790800001</v>
       </c>
       <c r="Q92">
-        <v>-17.85450892</v>
+        <v>-18.64204790800001</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.6126055868605952</v>
+        <v>0.6755839854006614</v>
       </c>
       <c r="T92">
-        <v>9.55715647962376</v>
+        <v>10.61906275513751</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.06913689459143324</v>
+        <v>0.06837714849702188</v>
       </c>
       <c r="W92">
-        <v>0.2194975202553401</v>
+        <v>0.2196766683844023</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8863,7 +8863,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3840938588412958</v>
+        <v>0.3798730472056771</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8871,22 +8871,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2607083269158655</v>
+        <v>0.2626083269158656</v>
       </c>
       <c r="C93">
-        <v>-218.1127043232623</v>
+        <v>-223.03427672084</v>
       </c>
       <c r="D93">
-        <v>96.83029567673768</v>
+        <v>95.98172327915998</v>
       </c>
       <c r="E93">
-        <v>256.143</v>
+        <v>260.216</v>
       </c>
       <c r="F93">
-        <v>370.643</v>
+        <v>374.716</v>
       </c>
       <c r="G93">
         <v>55.7</v>
@@ -8907,37 +8907,37 @@
         <v>33.2</v>
       </c>
       <c r="M93">
-        <v>87.39761940000001</v>
+        <v>88.3580328</v>
       </c>
       <c r="N93">
-        <v>-54.19761940000001</v>
+        <v>-55.1580328</v>
       </c>
       <c r="O93">
-        <v>-9.755571492000001</v>
+        <v>-9.928445904</v>
       </c>
       <c r="P93">
-        <v>-44.44204790800001</v>
+        <v>-45.229586896</v>
       </c>
       <c r="Q93">
-        <v>-18.64204790800001</v>
+        <v>-19.429586896</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.6755839854006614</v>
+        <v>0.7543069835757442</v>
       </c>
       <c r="T93">
-        <v>10.61906275513751</v>
+        <v>11.9464455995297</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.06837714849702188</v>
+        <v>0.06763391862205424</v>
       </c>
       <c r="W93">
-        <v>0.2196766683844023</v>
+        <v>0.2198519219889196</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8945,7 +8945,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3798730472056771</v>
+        <v>0.3757439923447459</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8953,22 +8953,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2626083269158656</v>
+        <v>0.2645083269158656</v>
       </c>
       <c r="C94">
-        <v>-223.03427672084</v>
+        <v>-227.9411053948647</v>
       </c>
       <c r="D94">
-        <v>95.98172327915998</v>
+        <v>95.14789460513532</v>
       </c>
       <c r="E94">
-        <v>260.216</v>
+        <v>264.289</v>
       </c>
       <c r="F94">
-        <v>374.716</v>
+        <v>378.789</v>
       </c>
       <c r="G94">
         <v>55.7</v>
@@ -8989,37 +8989,37 @@
         <v>33.2</v>
       </c>
       <c r="M94">
-        <v>88.3580328</v>
+        <v>89.31844620000001</v>
       </c>
       <c r="N94">
-        <v>-55.1580328</v>
+        <v>-56.11844620000001</v>
       </c>
       <c r="O94">
-        <v>-9.928445904</v>
+        <v>-10.101320316</v>
       </c>
       <c r="P94">
-        <v>-45.229586896</v>
+        <v>-46.01712588400001</v>
       </c>
       <c r="Q94">
-        <v>-19.429586896</v>
+        <v>-20.21712588400001</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.7543069835757442</v>
+        <v>0.8555222669437078</v>
       </c>
       <c r="T94">
-        <v>11.9464455995297</v>
+        <v>13.65308068517681</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.06763391862205424</v>
+        <v>0.06690667218525796</v>
       </c>
       <c r="W94">
-        <v>0.2198519219889196</v>
+        <v>0.2200234066987162</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3757439923447459</v>
+        <v>0.3717037343625442</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9035,22 +9035,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2645083269158656</v>
+        <v>0.2664083269158656</v>
       </c>
       <c r="C95">
-        <v>-227.9411053948647</v>
+        <v>-232.8335712884559</v>
       </c>
       <c r="D95">
-        <v>95.14789460513532</v>
+        <v>94.32842871154418</v>
       </c>
       <c r="E95">
-        <v>264.289</v>
+        <v>268.362</v>
       </c>
       <c r="F95">
-        <v>378.789</v>
+        <v>382.862</v>
       </c>
       <c r="G95">
         <v>55.7</v>
@@ -9071,37 +9071,37 @@
         <v>33.2</v>
       </c>
       <c r="M95">
-        <v>89.31844620000001</v>
+        <v>90.2788596</v>
       </c>
       <c r="N95">
-        <v>-56.11844620000001</v>
+        <v>-57.0788596</v>
       </c>
       <c r="O95">
-        <v>-10.101320316</v>
+        <v>-10.274194728</v>
       </c>
       <c r="P95">
-        <v>-46.01712588400001</v>
+        <v>-46.804664872</v>
       </c>
       <c r="Q95">
-        <v>-20.21712588400001</v>
+        <v>-21.004664872</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.8555222669437078</v>
+        <v>0.9904759781009926</v>
       </c>
       <c r="T95">
-        <v>13.65308068517681</v>
+        <v>15.92859413270628</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.06690667218525796</v>
+        <v>0.06619489907690417</v>
       </c>
       <c r="W95">
-        <v>0.2200234066987162</v>
+        <v>0.220191242797666</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3717037343625442</v>
+        <v>0.3677494393161342</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9117,22 +9117,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2664083269158656</v>
+        <v>0.2683083269158656</v>
       </c>
       <c r="C96">
-        <v>-232.8335712884559</v>
+        <v>-237.7120423332303</v>
       </c>
       <c r="D96">
-        <v>94.32842871154418</v>
+        <v>93.52295766676976</v>
       </c>
       <c r="E96">
-        <v>268.362</v>
+        <v>272.4350000000001</v>
       </c>
       <c r="F96">
-        <v>382.862</v>
+        <v>386.9350000000001</v>
       </c>
       <c r="G96">
         <v>55.7</v>
@@ -9153,37 +9153,37 @@
         <v>33.2</v>
       </c>
       <c r="M96">
-        <v>90.2788596</v>
+        <v>91.23927300000001</v>
       </c>
       <c r="N96">
-        <v>-57.0788596</v>
+        <v>-58.03927300000001</v>
       </c>
       <c r="O96">
-        <v>-10.274194728</v>
+        <v>-10.44706914</v>
       </c>
       <c r="P96">
-        <v>-46.804664872</v>
+        <v>-47.59220386000001</v>
       </c>
       <c r="Q96">
-        <v>-21.004664872</v>
+        <v>-21.79220386</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.9904759781009926</v>
+        <v>1.179411173721192</v>
       </c>
       <c r="T96">
-        <v>15.92859413270628</v>
+        <v>19.11431295924755</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.06619489907690417</v>
+        <v>0.06549811066556832</v>
       </c>
       <c r="W96">
-        <v>0.220191242797666</v>
+        <v>0.220355545505059</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3677494393161342</v>
+        <v>0.3638783925864907</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9199,22 +9199,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2683083269158656</v>
+        <v>0.2702083269158656</v>
       </c>
       <c r="C97">
-        <v>-237.7120423332303</v>
+        <v>-242.5768740001251</v>
       </c>
       <c r="D97">
-        <v>93.52295766676976</v>
+        <v>92.73112599987495</v>
       </c>
       <c r="E97">
-        <v>272.4350000000001</v>
+        <v>276.508</v>
       </c>
       <c r="F97">
-        <v>386.9350000000001</v>
+        <v>391.008</v>
       </c>
       <c r="G97">
         <v>55.7</v>
@@ -9235,37 +9235,37 @@
         <v>33.2</v>
       </c>
       <c r="M97">
-        <v>91.23927300000001</v>
+        <v>92.19968640000002</v>
       </c>
       <c r="N97">
-        <v>-58.03927300000001</v>
+        <v>-58.99968640000002</v>
       </c>
       <c r="O97">
-        <v>-10.44706914</v>
+        <v>-10.619943552</v>
       </c>
       <c r="P97">
-        <v>-47.59220386000001</v>
+        <v>-48.37974284800001</v>
       </c>
       <c r="Q97">
-        <v>-21.79220386</v>
+        <v>-22.57974284800001</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.179411173721192</v>
+        <v>1.462813967151491</v>
       </c>
       <c r="T97">
-        <v>19.11431295924755</v>
+        <v>23.89289119905944</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.06549811066556832</v>
+        <v>0.06481583867946865</v>
       </c>
       <c r="W97">
-        <v>0.220355545505059</v>
+        <v>0.2205164252393813</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9273,7 +9273,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3638783925864907</v>
+        <v>0.3600879926637147</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9281,22 +9281,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2702083269158655</v>
+        <v>0.2721083269158656</v>
       </c>
       <c r="C98">
-        <v>-242.576874000125</v>
+        <v>-247.4284098224736</v>
       </c>
       <c r="D98">
-        <v>92.73112599987499</v>
+        <v>91.95259017752643</v>
       </c>
       <c r="E98">
-        <v>276.508</v>
+        <v>280.581</v>
       </c>
       <c r="F98">
-        <v>391.008</v>
+        <v>395.081</v>
       </c>
       <c r="G98">
         <v>55.7</v>
@@ -9317,37 +9317,37 @@
         <v>33.2</v>
       </c>
       <c r="M98">
-        <v>92.1996864</v>
+        <v>93.16009980000001</v>
       </c>
       <c r="N98">
-        <v>-58.9996864</v>
+        <v>-59.96009980000001</v>
       </c>
       <c r="O98">
-        <v>-10.619943552</v>
+        <v>-10.792817964</v>
       </c>
       <c r="P98">
-        <v>-48.379742848</v>
+        <v>-49.16728183600001</v>
       </c>
       <c r="Q98">
-        <v>-22.579742848</v>
+        <v>-23.36728183600001</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.462813967151487</v>
+        <v>1.935151956201982</v>
       </c>
       <c r="T98">
-        <v>23.89289119905938</v>
+        <v>31.8571882654125</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.06481583867946866</v>
+        <v>0.06414763415699989</v>
       </c>
       <c r="W98">
-        <v>0.2205164252393813</v>
+        <v>0.2206739878657794</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9355,7 +9355,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3600879926637147</v>
+        <v>0.3563757453166662</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9363,22 +9363,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2721083269158656</v>
+        <v>0.2740083269158656</v>
       </c>
       <c r="C99">
-        <v>-247.4284098224736</v>
+        <v>-252.2669818929515</v>
       </c>
       <c r="D99">
-        <v>91.95259017752643</v>
+        <v>91.18701810704843</v>
       </c>
       <c r="E99">
-        <v>280.581</v>
+        <v>284.654</v>
       </c>
       <c r="F99">
-        <v>395.081</v>
+        <v>399.154</v>
       </c>
       <c r="G99">
         <v>55.7</v>
@@ -9399,37 +9399,37 @@
         <v>33.2</v>
       </c>
       <c r="M99">
-        <v>93.16009980000001</v>
+        <v>94.1205132</v>
       </c>
       <c r="N99">
-        <v>-59.96009980000001</v>
+        <v>-60.9205132</v>
       </c>
       <c r="O99">
-        <v>-10.792817964</v>
+        <v>-10.965692376</v>
       </c>
       <c r="P99">
-        <v>-49.16728183600001</v>
+        <v>-49.954820824</v>
       </c>
       <c r="Q99">
-        <v>-23.36728183600001</v>
+        <v>-24.154820824</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.935151956201982</v>
+        <v>2.879827934302973</v>
       </c>
       <c r="T99">
-        <v>31.8571882654125</v>
+        <v>47.78578239811876</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.06414763415699989</v>
+        <v>0.06349306646152031</v>
       </c>
       <c r="W99">
-        <v>0.2206739878657794</v>
+        <v>0.2208283349283735</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3563757453166662</v>
+        <v>0.3527392581195573</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9445,22 +9445,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2740083269158656</v>
+        <v>0.2759083269158655</v>
       </c>
       <c r="C100">
-        <v>-252.2669818929515</v>
+        <v>-257.0929113359036</v>
       </c>
       <c r="D100">
-        <v>91.18701810704843</v>
+        <v>90.43408866409641</v>
       </c>
       <c r="E100">
-        <v>284.654</v>
+        <v>288.727</v>
       </c>
       <c r="F100">
-        <v>399.154</v>
+        <v>403.227</v>
       </c>
       <c r="G100">
         <v>55.7</v>
@@ -9481,37 +9481,37 @@
         <v>33.2</v>
       </c>
       <c r="M100">
-        <v>94.1205132</v>
+        <v>95.08092660000001</v>
       </c>
       <c r="N100">
-        <v>-60.9205132</v>
+        <v>-61.88092660000001</v>
       </c>
       <c r="O100">
-        <v>-10.965692376</v>
+        <v>-11.138566788</v>
       </c>
       <c r="P100">
-        <v>-49.954820824</v>
+        <v>-50.742359812</v>
       </c>
       <c r="Q100">
-        <v>-24.154820824</v>
+        <v>-24.942359812</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.879827934302973</v>
+        <v>5.713855868605947</v>
       </c>
       <c r="T100">
-        <v>47.78578239811876</v>
+        <v>95.57156479623751</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.06349306646152031</v>
+        <v>0.06285172235584838</v>
       </c>
       <c r="W100">
-        <v>0.2208283349283735</v>
+        <v>0.220979563868491</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9519,91 +9519,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3527392581195573</v>
+        <v>0.3491762353102689</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2759083269158655</v>
-      </c>
-      <c r="C101">
-        <v>-257.0929113359036</v>
-      </c>
-      <c r="D101">
-        <v>90.43408866409641</v>
-      </c>
-      <c r="E101">
-        <v>288.727</v>
-      </c>
-      <c r="F101">
-        <v>403.227</v>
-      </c>
-      <c r="G101">
-        <v>55.7</v>
-      </c>
-      <c r="H101">
-        <v>292.8</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>59</v>
-      </c>
-      <c r="K101">
-        <v>25.8</v>
-      </c>
-      <c r="L101">
-        <v>33.2</v>
-      </c>
-      <c r="M101">
-        <v>95.08092660000001</v>
-      </c>
-      <c r="N101">
-        <v>-61.88092660000001</v>
-      </c>
-      <c r="O101">
-        <v>-11.138566788</v>
-      </c>
-      <c r="P101">
-        <v>-50.742359812</v>
-      </c>
-      <c r="Q101">
-        <v>-24.942359812</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>5.713855868605947</v>
-      </c>
-      <c r="T101">
-        <v>95.57156479623751</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.06285172235584838</v>
-      </c>
-      <c r="W101">
-        <v>0.220979563868491</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.3491762353102689</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
